--- a/data/nzd0259/nzd0259.xlsx
+++ b/data/nzd0259/nzd0259.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U340"/>
+  <dimension ref="A1:U341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23862,6 +23862,75 @@
       <c r="U340" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:42+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>344.9</v>
+      </c>
+      <c r="C341" t="n">
+        <v>323.54</v>
+      </c>
+      <c r="D341" t="n">
+        <v>304.64</v>
+      </c>
+      <c r="E341" t="n">
+        <v>307.5</v>
+      </c>
+      <c r="F341" t="n">
+        <v>294.45</v>
+      </c>
+      <c r="G341" t="n">
+        <v>317.04</v>
+      </c>
+      <c r="H341" t="n">
+        <v>328.48</v>
+      </c>
+      <c r="I341" t="n">
+        <v>333.25</v>
+      </c>
+      <c r="J341" t="n">
+        <v>341.14</v>
+      </c>
+      <c r="K341" t="n">
+        <v>341.42</v>
+      </c>
+      <c r="L341" t="n">
+        <v>336.14</v>
+      </c>
+      <c r="M341" t="n">
+        <v>345.24</v>
+      </c>
+      <c r="N341" t="n">
+        <v>350.22</v>
+      </c>
+      <c r="O341" t="n">
+        <v>352.09</v>
+      </c>
+      <c r="P341" t="n">
+        <v>354.16</v>
+      </c>
+      <c r="Q341" t="n">
+        <v>352.94</v>
+      </c>
+      <c r="R341" t="n">
+        <v>349.44</v>
+      </c>
+      <c r="S341" t="n">
+        <v>335</v>
+      </c>
+      <c r="T341" t="n">
+        <v>309.17</v>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -23876,7 +23945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B348"/>
+  <dimension ref="A1:B349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27359,6 +27428,16 @@
       </c>
       <c r="B348" t="n">
         <v>-0.57</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -27527,28 +27606,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09001357480864333</v>
+        <v>-0.09028263163668244</v>
       </c>
       <c r="J2" t="n">
+        <v>340</v>
+      </c>
+      <c r="K2" t="n">
         <v>339</v>
       </c>
-      <c r="K2" t="n">
-        <v>338</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.01305246588937903</v>
+        <v>0.01320097366267048</v>
       </c>
       <c r="M2" t="n">
-        <v>3.962445061488571</v>
+        <v>3.952138776166466</v>
       </c>
       <c r="N2" t="n">
-        <v>33.23642054757046</v>
+        <v>33.13908980354851</v>
       </c>
       <c r="O2" t="n">
-        <v>5.765103689229749</v>
+        <v>5.756656130389283</v>
       </c>
       <c r="P2" t="n">
-        <v>347.7305927300334</v>
+        <v>347.7334151665003</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -27609,28 +27688,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08218801997113184</v>
+        <v>-0.08059829657993689</v>
       </c>
       <c r="J3" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K3" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01421042730782796</v>
+        <v>0.01373489961410079</v>
       </c>
       <c r="M3" t="n">
-        <v>4.101677829969918</v>
+        <v>4.099327262271856</v>
       </c>
       <c r="N3" t="n">
-        <v>25.41094466464851</v>
+        <v>25.36101008098424</v>
       </c>
       <c r="O3" t="n">
-        <v>5.040926964819914</v>
+        <v>5.035971612408497</v>
       </c>
       <c r="P3" t="n">
-        <v>322.7558566280589</v>
+        <v>322.7391919793901</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -27691,28 +27770,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0407581512921976</v>
+        <v>-0.03948332767821545</v>
       </c>
       <c r="J4" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K4" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001732652013634484</v>
+        <v>0.001634623991245587</v>
       </c>
       <c r="M4" t="n">
-        <v>5.808230218267937</v>
+        <v>5.798011673846893</v>
       </c>
       <c r="N4" t="n">
-        <v>51.90284511254569</v>
+        <v>51.76614002200842</v>
       </c>
       <c r="O4" t="n">
-        <v>7.204362922045619</v>
+        <v>7.194869006591324</v>
       </c>
       <c r="P4" t="n">
-        <v>303.355229618264</v>
+        <v>303.3418659804391</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -27773,28 +27852,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2379330488784411</v>
+        <v>0.2388015978269941</v>
       </c>
       <c r="J5" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K5" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06394553585080631</v>
+        <v>0.06470670221270847</v>
       </c>
       <c r="M5" t="n">
-        <v>4.736789460023101</v>
+        <v>4.727637482689013</v>
       </c>
       <c r="N5" t="n">
-        <v>44.93938444458701</v>
+        <v>44.81461364520681</v>
       </c>
       <c r="O5" t="n">
-        <v>6.703684393271137</v>
+        <v>6.69437178868987</v>
       </c>
       <c r="P5" t="n">
-        <v>299.7281517564048</v>
+        <v>299.7190469881415</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -27855,28 +27934,28 @@
         <v>0.1324</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3425994959030169</v>
+        <v>0.3406114210455186</v>
       </c>
       <c r="J6" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K6" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03951885959315038</v>
+        <v>0.03927803436538757</v>
       </c>
       <c r="M6" t="n">
-        <v>9.993010539200643</v>
+        <v>9.97555105716091</v>
       </c>
       <c r="N6" t="n">
-        <v>153.2289923859894</v>
+        <v>152.8127056173249</v>
       </c>
       <c r="O6" t="n">
-        <v>12.37856988452177</v>
+        <v>12.36174363175862</v>
       </c>
       <c r="P6" t="n">
-        <v>289.1695706814289</v>
+        <v>289.1905959710261</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27933,28 +28012,28 @@
         <v>0.1253</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3668219929435733</v>
+        <v>0.3692303746686491</v>
       </c>
       <c r="J7" t="n">
+        <v>340</v>
+      </c>
+      <c r="K7" t="n">
         <v>339</v>
       </c>
-      <c r="K7" t="n">
-        <v>338</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1005211084871286</v>
+        <v>0.1021354394353977</v>
       </c>
       <c r="M7" t="n">
-        <v>5.832377448685516</v>
+        <v>5.827949845309448</v>
       </c>
       <c r="N7" t="n">
-        <v>65.36584277852003</v>
+        <v>65.23010188791477</v>
       </c>
       <c r="O7" t="n">
-        <v>8.084914518937108</v>
+        <v>8.076515454570416</v>
       </c>
       <c r="P7" t="n">
-        <v>303.0983704067909</v>
+        <v>303.0731188735917</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28011,28 +28090,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2131397753336974</v>
+        <v>0.2187053031460086</v>
       </c>
       <c r="J8" t="n">
+        <v>340</v>
+      </c>
+      <c r="K8" t="n">
         <v>339</v>
       </c>
-      <c r="K8" t="n">
-        <v>338</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.0466970762453881</v>
+        <v>0.04902142754406857</v>
       </c>
       <c r="M8" t="n">
-        <v>5.410450747278647</v>
+        <v>5.422595503254088</v>
       </c>
       <c r="N8" t="n">
-        <v>50.31146567694509</v>
+        <v>50.4676187777812</v>
       </c>
       <c r="O8" t="n">
-        <v>7.093057568985683</v>
+        <v>7.104056501589863</v>
       </c>
       <c r="P8" t="n">
-        <v>312.7437974098382</v>
+        <v>312.6854143954791</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28089,28 +28168,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.250360277350784</v>
+        <v>0.25588669759087</v>
       </c>
       <c r="J9" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K9" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03898997806890592</v>
+        <v>0.04073378808180639</v>
       </c>
       <c r="M9" t="n">
-        <v>6.857103248415131</v>
+        <v>6.86479134577479</v>
       </c>
       <c r="N9" t="n">
-        <v>84.1606021270517</v>
+        <v>84.21331163787355</v>
       </c>
       <c r="O9" t="n">
-        <v>9.173908770368916</v>
+        <v>9.176781115286206</v>
       </c>
       <c r="P9" t="n">
-        <v>316.6146113784541</v>
+        <v>316.5567012506297</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28167,28 +28246,28 @@
         <v>0.1406</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4722341543496871</v>
+        <v>0.4766750906544979</v>
       </c>
       <c r="J10" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K10" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1518111631764815</v>
+        <v>0.1545857751715934</v>
       </c>
       <c r="M10" t="n">
-        <v>6.37434630158207</v>
+        <v>6.376442580452716</v>
       </c>
       <c r="N10" t="n">
-        <v>66.8474874982175</v>
+        <v>66.83974088723798</v>
       </c>
       <c r="O10" t="n">
-        <v>8.176031280408454</v>
+        <v>8.175557527608621</v>
       </c>
       <c r="P10" t="n">
-        <v>320.8337792239174</v>
+        <v>320.7867525990929</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28245,28 +28324,28 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3362552572323016</v>
+        <v>0.3371884402913038</v>
       </c>
       <c r="J11" t="n">
+        <v>340</v>
+      </c>
+      <c r="K11" t="n">
         <v>339</v>
       </c>
-      <c r="K11" t="n">
-        <v>338</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.074743318904814</v>
+        <v>0.07550383520140613</v>
       </c>
       <c r="M11" t="n">
-        <v>6.271568341033031</v>
+        <v>6.257887200718682</v>
       </c>
       <c r="N11" t="n">
-        <v>76.06398752528474</v>
+        <v>75.84818737187078</v>
       </c>
       <c r="O11" t="n">
-        <v>8.721467051206737</v>
+        <v>8.709086483200794</v>
       </c>
       <c r="P11" t="n">
-        <v>330.9829650152823</v>
+        <v>330.9731883554363</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28323,28 +28402,28 @@
         <v>0.1507</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3836206492335407</v>
+        <v>0.3812734453165331</v>
       </c>
       <c r="J12" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K12" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L12" t="n">
-        <v>0.09173650211368256</v>
+        <v>0.0911187622793117</v>
       </c>
       <c r="M12" t="n">
-        <v>6.919539476015515</v>
+        <v>6.911875997854054</v>
       </c>
       <c r="N12" t="n">
-        <v>79.0133232508239</v>
+        <v>78.83500298085993</v>
       </c>
       <c r="O12" t="n">
-        <v>8.888943877133205</v>
+        <v>8.878907758325903</v>
       </c>
       <c r="P12" t="n">
-        <v>330.4857632138427</v>
+        <v>330.5103683299577</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28401,28 +28480,28 @@
         <v>0.1363</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2437361104810054</v>
+        <v>0.2465132237203426</v>
       </c>
       <c r="J13" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K13" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03510339205093671</v>
+        <v>0.03604182553846924</v>
       </c>
       <c r="M13" t="n">
-        <v>7.737238591308672</v>
+        <v>7.729250895979376</v>
       </c>
       <c r="N13" t="n">
-        <v>87.2523307202658</v>
+        <v>87.0684320186742</v>
       </c>
       <c r="O13" t="n">
-        <v>9.340895605896996</v>
+        <v>9.331046673266306</v>
       </c>
       <c r="P13" t="n">
-        <v>333.8816285834006</v>
+        <v>333.8521915611681</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28479,28 +28558,28 @@
         <v>0.0713</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4760273744063004</v>
+        <v>0.4774740468980929</v>
       </c>
       <c r="J14" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K14" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1307456116771637</v>
+        <v>0.1320399425096782</v>
       </c>
       <c r="M14" t="n">
-        <v>7.190583470698753</v>
+        <v>7.177130390943439</v>
       </c>
       <c r="N14" t="n">
-        <v>81.69779190782178</v>
+        <v>81.4780447410664</v>
       </c>
       <c r="O14" t="n">
-        <v>9.038683084820585</v>
+        <v>9.026518971401234</v>
       </c>
       <c r="P14" t="n">
-        <v>335.2123263807791</v>
+        <v>335.1971612967475</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28557,28 +28636,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4250615948104308</v>
+        <v>0.4268332800252383</v>
       </c>
       <c r="J15" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K15" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1012494420466257</v>
+        <v>0.1024834327239919</v>
       </c>
       <c r="M15" t="n">
-        <v>7.308948845981083</v>
+        <v>7.296546918196245</v>
       </c>
       <c r="N15" t="n">
-        <v>86.97150016774985</v>
+        <v>86.7465081666606</v>
       </c>
       <c r="O15" t="n">
-        <v>9.325851176581677</v>
+        <v>9.313780551777061</v>
       </c>
       <c r="P15" t="n">
-        <v>337.8046185618311</v>
+        <v>337.7860464556269</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28635,28 +28714,28 @@
         <v>0.079</v>
       </c>
       <c r="I16" t="n">
-        <v>0.246348710080206</v>
+        <v>0.2488266698875596</v>
       </c>
       <c r="J16" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K16" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L16" t="n">
-        <v>0.03011251197145681</v>
+        <v>0.03085043591404102</v>
       </c>
       <c r="M16" t="n">
-        <v>8.235096597985258</v>
+        <v>8.224251466575875</v>
       </c>
       <c r="N16" t="n">
-        <v>105.998970802359</v>
+        <v>105.7474731520529</v>
       </c>
       <c r="O16" t="n">
-        <v>10.29558015860976</v>
+        <v>10.2833590403162</v>
       </c>
       <c r="P16" t="n">
-        <v>343.2236226800665</v>
+        <v>343.1976468846332</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28713,28 +28792,28 @@
         <v>0.1836</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3363697965507754</v>
+        <v>0.3377165591653365</v>
       </c>
       <c r="J17" t="n">
+        <v>340</v>
+      </c>
+      <c r="K17" t="n">
         <v>339</v>
       </c>
-      <c r="K17" t="n">
-        <v>338</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.039960045240377</v>
+        <v>0.04047677329534771</v>
       </c>
       <c r="M17" t="n">
-        <v>10.05228610557221</v>
+        <v>10.0303517844014</v>
       </c>
       <c r="N17" t="n">
-        <v>147.7230932138363</v>
+        <v>147.3051969013899</v>
       </c>
       <c r="O17" t="n">
-        <v>12.15413893345951</v>
+        <v>12.13693523511557</v>
       </c>
       <c r="P17" t="n">
-        <v>341.7415256297132</v>
+        <v>341.727416029406</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28791,28 +28870,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4725751693079041</v>
+        <v>0.4730944501206394</v>
       </c>
       <c r="J18" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K18" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L18" t="n">
-        <v>0.06256492795972535</v>
+        <v>0.063022752869906</v>
       </c>
       <c r="M18" t="n">
-        <v>10.17127943068188</v>
+        <v>10.1435927142777</v>
       </c>
       <c r="N18" t="n">
-        <v>173.8212019332385</v>
+        <v>173.3032811257572</v>
       </c>
       <c r="O18" t="n">
-        <v>13.18412689309529</v>
+        <v>13.16447040810063</v>
       </c>
       <c r="P18" t="n">
-        <v>336.260602115982</v>
+        <v>336.2549821865137</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -28873,28 +28952,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.65802009566372</v>
+        <v>1.661383183008483</v>
       </c>
       <c r="J19" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K19" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1331229254740744</v>
+        <v>0.134216965533382</v>
       </c>
       <c r="M19" t="n">
-        <v>26.87343674561195</v>
+        <v>26.80728248327377</v>
       </c>
       <c r="N19" t="n">
-        <v>962.1407701029211</v>
+        <v>959.3790110790261</v>
       </c>
       <c r="O19" t="n">
-        <v>31.0183940606686</v>
+        <v>30.97384398293221</v>
       </c>
       <c r="P19" t="n">
-        <v>285.8660012604889</v>
+        <v>285.8303790317644</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -28955,28 +29034,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8897601313048772</v>
+        <v>0.889255549291006</v>
       </c>
       <c r="J20" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K20" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05109898656675682</v>
+        <v>0.05131247321995669</v>
       </c>
       <c r="M20" t="n">
-        <v>23.96944651263223</v>
+        <v>23.90118353249121</v>
       </c>
       <c r="N20" t="n">
-        <v>785.8141596947769</v>
+        <v>783.477886669802</v>
       </c>
       <c r="O20" t="n">
-        <v>28.03237698973772</v>
+        <v>27.99067499489432</v>
       </c>
       <c r="P20" t="n">
-        <v>286.9927202020817</v>
+        <v>286.9980779916104</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -29018,7 +29097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U340"/>
+  <dimension ref="A1:U341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65273,6 +65352,113 @@
         </is>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:42+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>-38.463712488880965,174.64400365194365</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>-38.46300445506299,174.6442369252406</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>-38.4622969558377,174.6444420123062</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>-38.46159424248235,174.6443978179163</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>-38.46088801793002,174.6445358834532</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>-38.46018963644579,174.64426567090095</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>-38.45948879198225,174.64412319130247</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>-38.45878647163663,174.64405712117713</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>-38.458084214137486,174.6439553209138</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>-38.457377272444994,174.64393271584723</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>-38.4566683897028,174.6439305527524</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>-38.45597326970839,174.64376429901085</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>-38.4552751364348,174.64364509989483</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>-38.454574726987985,174.64356141942295</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>-38.4538744566211,174.6434754552952</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>-38.453169456879905,174.64342711146492</t>
+        </is>
+      </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>-38.452473055358944,174.64328089605866</t>
+        </is>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>-38.45175725381193,174.6431920314964</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>-38.4510143464244,174.64322887911806</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0259/nzd0259.xlsx
+++ b/data/nzd0259/nzd0259.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U341"/>
+  <dimension ref="A1:U343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23931,6 +23931,144 @@
       <c r="U341" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:49+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>347.26</v>
+      </c>
+      <c r="C342" t="n">
+        <v>326.54</v>
+      </c>
+      <c r="D342" t="n">
+        <v>309.6</v>
+      </c>
+      <c r="E342" t="n">
+        <v>309.33</v>
+      </c>
+      <c r="F342" t="n">
+        <v>299.25</v>
+      </c>
+      <c r="G342" t="n">
+        <v>316.18</v>
+      </c>
+      <c r="H342" t="n">
+        <v>326.6</v>
+      </c>
+      <c r="I342" t="n">
+        <v>332.3</v>
+      </c>
+      <c r="J342" t="n">
+        <v>340.66</v>
+      </c>
+      <c r="K342" t="n">
+        <v>341.44</v>
+      </c>
+      <c r="L342" t="n">
+        <v>336.95</v>
+      </c>
+      <c r="M342" t="n">
+        <v>344.53</v>
+      </c>
+      <c r="N342" t="n">
+        <v>350.21</v>
+      </c>
+      <c r="O342" t="n">
+        <v>351.57</v>
+      </c>
+      <c r="P342" t="n">
+        <v>354.78</v>
+      </c>
+      <c r="Q342" t="n">
+        <v>352.22</v>
+      </c>
+      <c r="R342" t="n">
+        <v>349</v>
+      </c>
+      <c r="S342" t="n">
+        <v>335.68</v>
+      </c>
+      <c r="T342" t="n">
+        <v>312.54</v>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>347.35</v>
+      </c>
+      <c r="C343" t="n">
+        <v>327.41</v>
+      </c>
+      <c r="D343" t="n">
+        <v>310.17</v>
+      </c>
+      <c r="E343" t="n">
+        <v>309.85</v>
+      </c>
+      <c r="F343" t="n">
+        <v>301.24</v>
+      </c>
+      <c r="G343" t="n">
+        <v>316.49</v>
+      </c>
+      <c r="H343" t="n">
+        <v>326.48</v>
+      </c>
+      <c r="I343" t="n">
+        <v>332.76</v>
+      </c>
+      <c r="J343" t="n">
+        <v>341.09</v>
+      </c>
+      <c r="K343" t="n">
+        <v>342.78</v>
+      </c>
+      <c r="L343" t="n">
+        <v>339.41</v>
+      </c>
+      <c r="M343" t="n">
+        <v>345.99</v>
+      </c>
+      <c r="N343" t="n">
+        <v>351.78</v>
+      </c>
+      <c r="O343" t="n">
+        <v>352.28</v>
+      </c>
+      <c r="P343" t="n">
+        <v>355.8</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>353.53</v>
+      </c>
+      <c r="R343" t="n">
+        <v>349.44</v>
+      </c>
+      <c r="S343" t="n">
+        <v>336.76</v>
+      </c>
+      <c r="T343" t="n">
+        <v>316.63</v>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -23945,7 +24083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B349"/>
+  <dimension ref="A1:B351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27438,6 +27576,26 @@
       </c>
       <c r="B349" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -27606,28 +27764,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09028263163668244</v>
+        <v>-0.08820202289734519</v>
       </c>
       <c r="J2" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K2" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01320097366267048</v>
+        <v>0.01273708381869487</v>
       </c>
       <c r="M2" t="n">
-        <v>3.952138776166466</v>
+        <v>3.940619355355139</v>
       </c>
       <c r="N2" t="n">
-        <v>33.13908980354851</v>
+        <v>32.96606674637441</v>
       </c>
       <c r="O2" t="n">
-        <v>5.756656130389283</v>
+        <v>5.741608376263084</v>
       </c>
       <c r="P2" t="n">
-        <v>347.7334151665003</v>
+        <v>347.7114915044785</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -27688,28 +27846,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08059829657993689</v>
+        <v>-0.07374723977743325</v>
       </c>
       <c r="J3" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K3" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01373489961410079</v>
+        <v>0.01154652140223189</v>
       </c>
       <c r="M3" t="n">
-        <v>4.099327262271856</v>
+        <v>4.117472043388355</v>
       </c>
       <c r="N3" t="n">
-        <v>25.36101008098424</v>
+        <v>25.44458931114607</v>
       </c>
       <c r="O3" t="n">
-        <v>5.035971612408497</v>
+        <v>5.044263009711733</v>
       </c>
       <c r="P3" t="n">
-        <v>322.7391919793901</v>
+        <v>322.6670500025771</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -27770,28 +27928,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03948332767821545</v>
+        <v>-0.03129339078408556</v>
       </c>
       <c r="J4" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K4" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001634623991245587</v>
+        <v>0.001032234797395892</v>
       </c>
       <c r="M4" t="n">
-        <v>5.798011673846893</v>
+        <v>5.807578509378294</v>
       </c>
       <c r="N4" t="n">
-        <v>51.76614002200842</v>
+        <v>51.79371495262614</v>
       </c>
       <c r="O4" t="n">
-        <v>7.194869006591324</v>
+        <v>7.196785042824757</v>
       </c>
       <c r="P4" t="n">
-        <v>303.3418659804391</v>
+        <v>303.2556285493588</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -27852,28 +28010,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2388015978269941</v>
+        <v>0.2427529915397036</v>
       </c>
       <c r="J5" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K5" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06470670221270847</v>
+        <v>0.06730449681938044</v>
       </c>
       <c r="M5" t="n">
-        <v>4.727637482689013</v>
+        <v>4.72142471751944</v>
       </c>
       <c r="N5" t="n">
-        <v>44.81461364520681</v>
+        <v>44.62968467473111</v>
       </c>
       <c r="O5" t="n">
-        <v>6.69437178868987</v>
+        <v>6.680545237832845</v>
       </c>
       <c r="P5" t="n">
-        <v>299.7190469881415</v>
+        <v>299.6774385794362</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -27934,28 +28092,28 @@
         <v>0.1324</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3406114210455186</v>
+        <v>0.342995618590239</v>
       </c>
       <c r="J6" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K6" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03927803436538757</v>
+        <v>0.04022424154678728</v>
       </c>
       <c r="M6" t="n">
-        <v>9.97555105716091</v>
+        <v>9.927606800156591</v>
       </c>
       <c r="N6" t="n">
-        <v>152.8127056173249</v>
+        <v>151.9445001138273</v>
       </c>
       <c r="O6" t="n">
-        <v>12.36174363175862</v>
+        <v>12.32657698283783</v>
       </c>
       <c r="P6" t="n">
-        <v>289.1905959710261</v>
+        <v>289.1652568950343</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28012,28 +28170,28 @@
         <v>0.1253</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3692303746686491</v>
+        <v>0.3731733168187308</v>
       </c>
       <c r="J7" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K7" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1021354394353977</v>
+        <v>0.1050224582274583</v>
       </c>
       <c r="M7" t="n">
-        <v>5.827949845309448</v>
+        <v>5.814388690327807</v>
       </c>
       <c r="N7" t="n">
-        <v>65.23010188791477</v>
+        <v>64.92429513362298</v>
       </c>
       <c r="O7" t="n">
-        <v>8.076515454570416</v>
+        <v>8.057561363937788</v>
       </c>
       <c r="P7" t="n">
-        <v>303.0731188735917</v>
+        <v>303.0315916173456</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28090,28 +28248,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2187053031460086</v>
+        <v>0.2275294910003428</v>
       </c>
       <c r="J8" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K8" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04902142754406857</v>
+        <v>0.05301503317247314</v>
       </c>
       <c r="M8" t="n">
-        <v>5.422595503254088</v>
+        <v>5.434941832425187</v>
       </c>
       <c r="N8" t="n">
-        <v>50.4676187777812</v>
+        <v>50.55529658089657</v>
       </c>
       <c r="O8" t="n">
-        <v>7.104056501589863</v>
+        <v>7.110224791164944</v>
       </c>
       <c r="P8" t="n">
-        <v>312.6854143954791</v>
+        <v>312.5924362822765</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28168,28 +28326,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.25588669759087</v>
+        <v>0.2659517708088637</v>
       </c>
       <c r="J9" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K9" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04073378808180639</v>
+        <v>0.04406866762105288</v>
       </c>
       <c r="M9" t="n">
-        <v>6.86479134577479</v>
+        <v>6.875033582983111</v>
       </c>
       <c r="N9" t="n">
-        <v>84.21331163787355</v>
+        <v>84.21937519751683</v>
       </c>
       <c r="O9" t="n">
-        <v>9.176781115286206</v>
+        <v>9.177111484422364</v>
       </c>
       <c r="P9" t="n">
-        <v>316.5567012506297</v>
+        <v>316.4507543365222</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28246,28 +28404,28 @@
         <v>0.1406</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4766750906544979</v>
+        <v>0.48507252993421</v>
       </c>
       <c r="J10" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K10" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1545857751715934</v>
+        <v>0.1600000775718201</v>
       </c>
       <c r="M10" t="n">
-        <v>6.376442580452716</v>
+        <v>6.380871276927111</v>
       </c>
       <c r="N10" t="n">
-        <v>66.83974088723798</v>
+        <v>66.78698386391719</v>
       </c>
       <c r="O10" t="n">
-        <v>8.175557527608621</v>
+        <v>8.172330381471198</v>
       </c>
       <c r="P10" t="n">
-        <v>320.7867525990929</v>
+        <v>320.6974320109837</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28324,28 +28482,28 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3371884402913038</v>
+        <v>0.3397353418469829</v>
       </c>
       <c r="J11" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K11" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07550383520140613</v>
+        <v>0.07731220387692617</v>
       </c>
       <c r="M11" t="n">
-        <v>6.257887200718682</v>
+        <v>6.234144269424967</v>
       </c>
       <c r="N11" t="n">
-        <v>75.84818737187078</v>
+        <v>75.43791323499556</v>
       </c>
       <c r="O11" t="n">
-        <v>8.709086483200794</v>
+        <v>8.685500171837864</v>
       </c>
       <c r="P11" t="n">
-        <v>330.9731883554363</v>
+        <v>330.9463778261503</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28402,28 +28560,28 @@
         <v>0.1507</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3812734453165331</v>
+        <v>0.3788324498299938</v>
       </c>
       <c r="J12" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K12" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0911187622793117</v>
+        <v>0.0909300935267674</v>
       </c>
       <c r="M12" t="n">
-        <v>6.911875997854054</v>
+        <v>6.884507288686615</v>
       </c>
       <c r="N12" t="n">
-        <v>78.83500298085993</v>
+        <v>78.412052952347</v>
       </c>
       <c r="O12" t="n">
-        <v>8.878907758325903</v>
+        <v>8.85505804342055</v>
       </c>
       <c r="P12" t="n">
-        <v>330.5103683299577</v>
+        <v>330.5360547014111</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28480,28 +28638,28 @@
         <v>0.1363</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2465132237203426</v>
+        <v>0.2519764655839398</v>
       </c>
       <c r="J13" t="n">
+        <v>342</v>
+      </c>
+      <c r="K13" t="n">
         <v>340</v>
       </c>
-      <c r="K13" t="n">
-        <v>338</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.03604182553846924</v>
+        <v>0.03793811242630152</v>
       </c>
       <c r="M13" t="n">
-        <v>7.729250895979376</v>
+        <v>7.712659560314219</v>
       </c>
       <c r="N13" t="n">
-        <v>87.0684320186742</v>
+        <v>86.70324511160683</v>
       </c>
       <c r="O13" t="n">
-        <v>9.331046673266306</v>
+        <v>9.311457732901269</v>
       </c>
       <c r="P13" t="n">
-        <v>333.8521915611681</v>
+        <v>333.7940181962425</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28558,28 +28716,28 @@
         <v>0.0713</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4774740468980929</v>
+        <v>0.4811162357716814</v>
       </c>
       <c r="J14" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K14" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1320399425096782</v>
+        <v>0.134978411305665</v>
       </c>
       <c r="M14" t="n">
-        <v>7.177130390943439</v>
+        <v>7.1542339533542</v>
       </c>
       <c r="N14" t="n">
-        <v>81.4780447410664</v>
+        <v>81.07024697478717</v>
       </c>
       <c r="O14" t="n">
-        <v>9.026518971401234</v>
+        <v>9.00390176394585</v>
       </c>
       <c r="P14" t="n">
-        <v>335.1971612967475</v>
+        <v>335.1588019935052</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28636,28 +28794,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4268332800252383</v>
+        <v>0.4301031413372614</v>
       </c>
       <c r="J15" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K15" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1024834327239919</v>
+        <v>0.1048713083117578</v>
       </c>
       <c r="M15" t="n">
-        <v>7.296546918196245</v>
+        <v>7.270595300291234</v>
       </c>
       <c r="N15" t="n">
-        <v>86.7465081666606</v>
+        <v>86.2924613902607</v>
       </c>
       <c r="O15" t="n">
-        <v>9.313780551777061</v>
+        <v>9.289373573619521</v>
       </c>
       <c r="P15" t="n">
-        <v>337.7860464556269</v>
+        <v>337.7516129581969</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28714,28 +28872,28 @@
         <v>0.079</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2488266698875596</v>
+        <v>0.2548990035665782</v>
       </c>
       <c r="J16" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K16" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L16" t="n">
-        <v>0.03085043591404102</v>
+        <v>0.03261789793050118</v>
       </c>
       <c r="M16" t="n">
-        <v>8.224251466575875</v>
+        <v>8.209228107045966</v>
       </c>
       <c r="N16" t="n">
-        <v>105.7474731520529</v>
+        <v>105.3118374462286</v>
       </c>
       <c r="O16" t="n">
-        <v>10.2833590403162</v>
+        <v>10.26215559452441</v>
       </c>
       <c r="P16" t="n">
-        <v>343.1976468846332</v>
+        <v>343.1337034038122</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28792,28 +28950,28 @@
         <v>0.1836</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3377165591653365</v>
+        <v>0.3402646660413987</v>
       </c>
       <c r="J17" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K17" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04047677329534771</v>
+        <v>0.04149208827555628</v>
       </c>
       <c r="M17" t="n">
-        <v>10.0303517844014</v>
+        <v>9.985938796213825</v>
       </c>
       <c r="N17" t="n">
-        <v>147.3051969013899</v>
+        <v>146.4757070244984</v>
       </c>
       <c r="O17" t="n">
-        <v>12.13693523511557</v>
+        <v>12.10271486173653</v>
       </c>
       <c r="P17" t="n">
-        <v>341.727416029406</v>
+        <v>341.7005930544758</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28870,28 +29028,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4730944501206394</v>
+        <v>0.4738177829017021</v>
       </c>
       <c r="J18" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K18" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L18" t="n">
-        <v>0.063022752869906</v>
+        <v>0.0638688176786123</v>
       </c>
       <c r="M18" t="n">
-        <v>10.1435927142777</v>
+        <v>10.08700697283271</v>
       </c>
       <c r="N18" t="n">
-        <v>173.3032811257572</v>
+        <v>172.274413178474</v>
       </c>
       <c r="O18" t="n">
-        <v>13.16447040810063</v>
+        <v>13.12533478348168</v>
       </c>
       <c r="P18" t="n">
-        <v>336.2549821865137</v>
+        <v>336.2471172899093</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -28952,28 +29110,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.661383183008483</v>
+        <v>1.669167481527216</v>
       </c>
       <c r="J19" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K19" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L19" t="n">
-        <v>0.134216965533382</v>
+        <v>0.1365652099380694</v>
       </c>
       <c r="M19" t="n">
-        <v>26.80728248327377</v>
+        <v>26.68021256816006</v>
       </c>
       <c r="N19" t="n">
-        <v>959.3790110790261</v>
+        <v>953.9828259861073</v>
       </c>
       <c r="O19" t="n">
-        <v>30.97384398293221</v>
+        <v>30.88661240709488</v>
       </c>
       <c r="P19" t="n">
-        <v>285.8303790317644</v>
+        <v>285.7475519012505</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -29034,28 +29192,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.889255549291006</v>
+        <v>0.8941190206153741</v>
       </c>
       <c r="J20" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K20" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05131247321995669</v>
+        <v>0.05238401828107331</v>
       </c>
       <c r="M20" t="n">
-        <v>23.90118353249121</v>
+        <v>23.78211025409155</v>
       </c>
       <c r="N20" t="n">
-        <v>783.477886669802</v>
+        <v>778.9804962007699</v>
       </c>
       <c r="O20" t="n">
-        <v>27.99067499489432</v>
+        <v>27.91022207365556</v>
       </c>
       <c r="P20" t="n">
-        <v>286.9980779916104</v>
+        <v>286.9461814485146</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -29097,7 +29255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U341"/>
+  <dimension ref="A1:U343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65459,6 +65617,220 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:49+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>-38.463713008601296,174.64397661556347</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>-38.463005115787006,174.64420255730124</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>-38.46229804832083,174.64438519120776</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>-38.461594645548175,174.64437685388359</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>-38.460889075201024,174.64448089636613</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>-38.4601894470394,174.64427552266034</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>-38.45948837795913,174.6441447274999</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>-38.458786262430955,174.644068003725</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>-38.45808408933874,174.64396081876376</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>-38.45737728274331,174.64393248705147</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>-38.456668980761854,174.6439213019357</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>-38.45597275163033,174.643772407675</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>-38.455275129138045,174.64364521410027</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>-38.45457434756065,174.64356735804964</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>-38.45387490900975,174.6434683746926</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>-38.45316848688553,174.64343526837305</t>
+        </is>
+      </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>-38.45247205678831,174.6432857749131</t>
+        </is>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>-38.451759003672365,174.64318456484423</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>-38.451023018554544,174.64319187565664</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>-38.46371302842101,174.6439755845151</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>-38.463005307395086,174.64419259059864</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>-38.46229817386652,174.64437866136362</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>-38.461594760079855,174.64437089689062</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>-38.460889513520414,174.64445809963556</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>-38.460189515313886,174.64427197144474</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>-38.45948835153199,174.6441461021508</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>-38.45878636373067,174.6440627342808</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>-38.458084201137616,174.6439558936065</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>-38.45737797272891,174.64391715773735</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>-38.45667077582562,174.64389320686178</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>-38.45597381697333,174.6437557335204</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>-38.455276274727375,174.6436272838438</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>-38.45457486562481,174.64355924954015</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>-38.4538756532611,174.64345672595906</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>-38.453170251736,174.6434204273317</t>
+        </is>
+      </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>-38.452473055358944,174.64328089605866</t>
+        </is>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>-38.45176178286155,174.643172706043</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>-38.45103354346855,174.6431469663988</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0259/nzd0259.xlsx
+++ b/data/nzd0259/nzd0259.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U343"/>
+  <dimension ref="A1:U344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24069,6 +24069,75 @@
       <c r="U343" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:26+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>350.48</v>
+      </c>
+      <c r="C344" t="n">
+        <v>331.7</v>
+      </c>
+      <c r="D344" t="n">
+        <v>321.44</v>
+      </c>
+      <c r="E344" t="n">
+        <v>313.3</v>
+      </c>
+      <c r="F344" t="n">
+        <v>311.76</v>
+      </c>
+      <c r="G344" t="n">
+        <v>318.2</v>
+      </c>
+      <c r="H344" t="n">
+        <v>325.98</v>
+      </c>
+      <c r="I344" t="n">
+        <v>334.18</v>
+      </c>
+      <c r="J344" t="n">
+        <v>343.76</v>
+      </c>
+      <c r="K344" t="n">
+        <v>344.75</v>
+      </c>
+      <c r="L344" t="n">
+        <v>341.82</v>
+      </c>
+      <c r="M344" t="n">
+        <v>348.87</v>
+      </c>
+      <c r="N344" t="n">
+        <v>353.7</v>
+      </c>
+      <c r="O344" t="n">
+        <v>352.7</v>
+      </c>
+      <c r="P344" t="n">
+        <v>355.66</v>
+      </c>
+      <c r="Q344" t="n">
+        <v>356.14</v>
+      </c>
+      <c r="R344" t="n">
+        <v>351.87</v>
+      </c>
+      <c r="S344" t="n">
+        <v>338.75</v>
+      </c>
+      <c r="T344" t="n">
+        <v>326.75</v>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -24083,7 +24152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B351"/>
+  <dimension ref="A1:B352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27596,6 +27665,16 @@
       </c>
       <c r="B351" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>
@@ -27764,28 +27843,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08820202289734519</v>
+        <v>-0.08545956527472678</v>
       </c>
       <c r="J2" t="n">
+        <v>343</v>
+      </c>
+      <c r="K2" t="n">
         <v>342</v>
       </c>
-      <c r="K2" t="n">
-        <v>341</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.01273708381869487</v>
+        <v>0.0120052091803633</v>
       </c>
       <c r="M2" t="n">
-        <v>3.940619355355139</v>
+        <v>3.944490572294025</v>
       </c>
       <c r="N2" t="n">
-        <v>32.96606674637441</v>
+        <v>32.9441674042267</v>
       </c>
       <c r="O2" t="n">
-        <v>5.741608376263084</v>
+        <v>5.739700985611245</v>
       </c>
       <c r="P2" t="n">
-        <v>347.7114915044785</v>
+        <v>347.6824666561936</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -27846,28 +27925,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07374723977743325</v>
+        <v>-0.06782025160708832</v>
       </c>
       <c r="J3" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K3" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01154652140223189</v>
+        <v>0.009704690969654206</v>
       </c>
       <c r="M3" t="n">
-        <v>4.117472043388355</v>
+        <v>4.141620676153729</v>
       </c>
       <c r="N3" t="n">
-        <v>25.44458931114607</v>
+        <v>25.71773852738018</v>
       </c>
       <c r="O3" t="n">
-        <v>5.044263009711733</v>
+        <v>5.071265968905613</v>
       </c>
       <c r="P3" t="n">
-        <v>322.6670500025771</v>
+        <v>322.6043677640329</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -27928,28 +28007,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03129339078408556</v>
+        <v>-0.02101719440831298</v>
       </c>
       <c r="J4" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K4" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001032234797395892</v>
+        <v>0.0004591758975710514</v>
       </c>
       <c r="M4" t="n">
-        <v>5.807578509378294</v>
+        <v>5.845192871614852</v>
       </c>
       <c r="N4" t="n">
-        <v>51.79371495262614</v>
+        <v>52.68681042964916</v>
       </c>
       <c r="O4" t="n">
-        <v>7.196785042824757</v>
+        <v>7.258568070194642</v>
       </c>
       <c r="P4" t="n">
-        <v>303.2556285493588</v>
+        <v>303.1469502503576</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -28010,28 +28089,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2427529915397036</v>
+        <v>0.2466905432027668</v>
       </c>
       <c r="J5" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K5" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06730449681938044</v>
+        <v>0.06948782411829912</v>
       </c>
       <c r="M5" t="n">
-        <v>4.72142471751944</v>
+        <v>4.728876427466006</v>
       </c>
       <c r="N5" t="n">
-        <v>44.62968467473111</v>
+        <v>44.65286426959975</v>
       </c>
       <c r="O5" t="n">
-        <v>6.680545237832845</v>
+        <v>6.682279870642934</v>
       </c>
       <c r="P5" t="n">
-        <v>299.6774385794362</v>
+        <v>299.6357960882534</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -28092,28 +28171,28 @@
         <v>0.1324</v>
       </c>
       <c r="I6" t="n">
-        <v>0.342995618590239</v>
+        <v>0.3504378619779697</v>
       </c>
       <c r="J6" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K6" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04022424154678728</v>
+        <v>0.04199354086384322</v>
       </c>
       <c r="M6" t="n">
-        <v>9.927606800156591</v>
+        <v>9.93209287137519</v>
       </c>
       <c r="N6" t="n">
-        <v>151.9445001138273</v>
+        <v>152.039574305067</v>
       </c>
       <c r="O6" t="n">
-        <v>12.32657698283783</v>
+        <v>12.33043285148851</v>
       </c>
       <c r="P6" t="n">
-        <v>289.1652568950343</v>
+        <v>289.0858521613936</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28170,28 +28249,28 @@
         <v>0.1253</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3731733168187308</v>
+        <v>0.3761042442912775</v>
       </c>
       <c r="J7" t="n">
+        <v>343</v>
+      </c>
+      <c r="K7" t="n">
         <v>342</v>
       </c>
-      <c r="K7" t="n">
-        <v>341</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1050224582274583</v>
+        <v>0.1069029229543783</v>
       </c>
       <c r="M7" t="n">
-        <v>5.814388690327807</v>
+        <v>5.812592773576632</v>
       </c>
       <c r="N7" t="n">
-        <v>64.92429513362298</v>
+        <v>64.81961172357772</v>
       </c>
       <c r="O7" t="n">
-        <v>8.057561363937788</v>
+        <v>8.051062769819753</v>
       </c>
       <c r="P7" t="n">
-        <v>303.0315916173456</v>
+        <v>303.0005874742016</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28248,28 +28327,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2275294910003428</v>
+        <v>0.2315577061802985</v>
       </c>
       <c r="J8" t="n">
+        <v>343</v>
+      </c>
+      <c r="K8" t="n">
         <v>342</v>
       </c>
-      <c r="K8" t="n">
-        <v>341</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.05301503317247314</v>
+        <v>0.05492613930970081</v>
       </c>
       <c r="M8" t="n">
-        <v>5.434941832425187</v>
+        <v>5.439056183079231</v>
       </c>
       <c r="N8" t="n">
-        <v>50.55529658089657</v>
+        <v>50.56819002980505</v>
       </c>
       <c r="O8" t="n">
-        <v>7.110224791164944</v>
+        <v>7.111131416997231</v>
       </c>
       <c r="P8" t="n">
-        <v>312.5924362822765</v>
+        <v>312.5498035963627</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28326,28 +28405,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2659517708088637</v>
+        <v>0.2717809445742567</v>
       </c>
       <c r="J9" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K9" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04406866762105288</v>
+        <v>0.04599660531774408</v>
       </c>
       <c r="M9" t="n">
-        <v>6.875033582983111</v>
+        <v>6.884348511476605</v>
       </c>
       <c r="N9" t="n">
-        <v>84.21937519751683</v>
+        <v>84.31057984354857</v>
       </c>
       <c r="O9" t="n">
-        <v>9.177111484422364</v>
+        <v>9.182079276697003</v>
       </c>
       <c r="P9" t="n">
-        <v>316.4507543365222</v>
+        <v>316.3891223985189</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28404,28 +28483,28 @@
         <v>0.1406</v>
       </c>
       <c r="I10" t="n">
-        <v>0.48507252993421</v>
+        <v>0.4907592853809884</v>
       </c>
       <c r="J10" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K10" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1600000775718201</v>
+        <v>0.163267810084379</v>
       </c>
       <c r="M10" t="n">
-        <v>6.380871276927111</v>
+        <v>6.39121904280919</v>
       </c>
       <c r="N10" t="n">
-        <v>66.78698386391719</v>
+        <v>66.90575921854065</v>
       </c>
       <c r="O10" t="n">
-        <v>8.172330381471198</v>
+        <v>8.179594074191009</v>
       </c>
       <c r="P10" t="n">
-        <v>320.6974320109837</v>
+        <v>320.6366786928298</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28482,28 +28561,28 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3397353418469829</v>
+        <v>0.342399445448184</v>
       </c>
       <c r="J11" t="n">
+        <v>343</v>
+      </c>
+      <c r="K11" t="n">
         <v>342</v>
       </c>
-      <c r="K11" t="n">
-        <v>341</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.07731220387692617</v>
+        <v>0.07876589377656418</v>
       </c>
       <c r="M11" t="n">
-        <v>6.234144269424967</v>
+        <v>6.229335064339679</v>
       </c>
       <c r="N11" t="n">
-        <v>75.43791323499556</v>
+        <v>75.28775575922138</v>
       </c>
       <c r="O11" t="n">
-        <v>8.685500171837864</v>
+        <v>8.676851719328928</v>
       </c>
       <c r="P11" t="n">
-        <v>330.9463778261503</v>
+        <v>330.9182180225387</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28560,28 +28639,28 @@
         <v>0.1507</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3788324498299938</v>
+        <v>0.3795795779237445</v>
       </c>
       <c r="J12" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K12" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0909300935267674</v>
+        <v>0.09170981231318687</v>
       </c>
       <c r="M12" t="n">
-        <v>6.884507288686615</v>
+        <v>6.868459912218909</v>
       </c>
       <c r="N12" t="n">
-        <v>78.412052952347</v>
+        <v>78.18896546062626</v>
       </c>
       <c r="O12" t="n">
-        <v>8.85505804342055</v>
+        <v>8.842452457357419</v>
       </c>
       <c r="P12" t="n">
-        <v>330.5360547014111</v>
+        <v>330.5281532749108</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28638,28 +28717,28 @@
         <v>0.1363</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2519764655839398</v>
+        <v>0.2566243008071205</v>
       </c>
       <c r="J13" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K13" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03793811242630152</v>
+        <v>0.03941349748793255</v>
       </c>
       <c r="M13" t="n">
-        <v>7.712659560314219</v>
+        <v>7.714522534602152</v>
       </c>
       <c r="N13" t="n">
-        <v>86.70324511160683</v>
+        <v>86.65846778125146</v>
       </c>
       <c r="O13" t="n">
-        <v>9.311457732901269</v>
+        <v>9.309053001312833</v>
       </c>
       <c r="P13" t="n">
-        <v>333.7940181962425</v>
+        <v>333.7443189795406</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28716,28 +28795,28 @@
         <v>0.0713</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4811162357716814</v>
+        <v>0.4843447243181391</v>
       </c>
       <c r="J14" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K14" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L14" t="n">
-        <v>0.134978411305665</v>
+        <v>0.1370499712029353</v>
       </c>
       <c r="M14" t="n">
-        <v>7.1542339533542</v>
+        <v>7.150088511206508</v>
       </c>
       <c r="N14" t="n">
-        <v>81.07024697478717</v>
+        <v>80.93694692787739</v>
       </c>
       <c r="O14" t="n">
-        <v>9.00390176394585</v>
+        <v>8.996496369580626</v>
       </c>
       <c r="P14" t="n">
-        <v>335.1588019935052</v>
+        <v>335.1246583638252</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28794,28 +28873,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4301031413372614</v>
+        <v>0.4321075049506231</v>
       </c>
       <c r="J15" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K15" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1048713083117578</v>
+        <v>0.1062273521579521</v>
       </c>
       <c r="M15" t="n">
-        <v>7.270595300291234</v>
+        <v>7.259540750049927</v>
       </c>
       <c r="N15" t="n">
-        <v>86.2924613902607</v>
+        <v>86.08060170596436</v>
       </c>
       <c r="O15" t="n">
-        <v>9.289373573619521</v>
+        <v>9.277963230470595</v>
       </c>
       <c r="P15" t="n">
-        <v>337.7516129581969</v>
+        <v>337.7304153457619</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28872,28 +28951,28 @@
         <v>0.079</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2548990035665782</v>
+        <v>0.258068401787076</v>
       </c>
       <c r="J16" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K16" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L16" t="n">
-        <v>0.03261789793050118</v>
+        <v>0.03355505814786264</v>
       </c>
       <c r="M16" t="n">
-        <v>8.209228107045966</v>
+        <v>8.202551563765011</v>
       </c>
       <c r="N16" t="n">
-        <v>105.3118374462286</v>
+        <v>105.1041242951151</v>
       </c>
       <c r="O16" t="n">
-        <v>10.26215559452441</v>
+        <v>10.25203025235075</v>
       </c>
       <c r="P16" t="n">
-        <v>343.1337034038122</v>
+        <v>343.1001846975842</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28950,28 +29029,28 @@
         <v>0.1836</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3402646660413987</v>
+        <v>0.3432626967543133</v>
       </c>
       <c r="J17" t="n">
+        <v>343</v>
+      </c>
+      <c r="K17" t="n">
         <v>342</v>
       </c>
-      <c r="K17" t="n">
-        <v>341</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.04149208827555628</v>
+        <v>0.04239429329883215</v>
       </c>
       <c r="M17" t="n">
-        <v>9.985938796213825</v>
+        <v>9.973840995658644</v>
       </c>
       <c r="N17" t="n">
-        <v>146.4757070244984</v>
+        <v>146.1365967155019</v>
       </c>
       <c r="O17" t="n">
-        <v>12.10271486173653</v>
+        <v>12.08869706442766</v>
       </c>
       <c r="P17" t="n">
-        <v>341.7005930544758</v>
+        <v>341.6689036126467</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29028,28 +29107,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4738177829017021</v>
+        <v>0.4756390806490796</v>
       </c>
       <c r="J18" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K18" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0638688176786123</v>
+        <v>0.06465618263954986</v>
       </c>
       <c r="M18" t="n">
-        <v>10.08700697283271</v>
+        <v>10.06651724543636</v>
       </c>
       <c r="N18" t="n">
-        <v>172.274413178474</v>
+        <v>171.7942118927017</v>
       </c>
       <c r="O18" t="n">
-        <v>13.12533478348168</v>
+        <v>13.10702910245879</v>
       </c>
       <c r="P18" t="n">
-        <v>336.2471172899093</v>
+        <v>336.2272361183441</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -29110,28 +29189,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.669167481527216</v>
+        <v>1.674300704836474</v>
       </c>
       <c r="J19" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K19" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1365652099380694</v>
+        <v>0.1379129515961157</v>
       </c>
       <c r="M19" t="n">
-        <v>26.68021256816006</v>
+        <v>26.6221175845404</v>
       </c>
       <c r="N19" t="n">
-        <v>953.9828259861073</v>
+        <v>951.4191653511458</v>
       </c>
       <c r="O19" t="n">
-        <v>30.88661240709488</v>
+        <v>30.84508332540448</v>
       </c>
       <c r="P19" t="n">
-        <v>285.7475519012505</v>
+        <v>285.6926944873234</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -29192,28 +29271,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8941190206153741</v>
+        <v>0.9031352821573018</v>
       </c>
       <c r="J20" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K20" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05238401828107331</v>
+        <v>0.05361789766049507</v>
       </c>
       <c r="M20" t="n">
-        <v>23.78211025409155</v>
+        <v>23.75290191408999</v>
       </c>
       <c r="N20" t="n">
-        <v>778.9804962007699</v>
+        <v>777.4735497453481</v>
       </c>
       <c r="O20" t="n">
-        <v>27.91022207365556</v>
+        <v>27.88321268694388</v>
       </c>
       <c r="P20" t="n">
-        <v>286.9461814485146</v>
+        <v>286.8495971286395</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -29255,7 +29334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U343"/>
+  <dimension ref="A1:U344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65831,6 +65910,113 @@
         </is>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:26+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>-38.46371371770118,174.6439397269421</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>-38.46300625220873,174.64414344444324</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>-38.46230065607248,174.644249553736</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>-38.461595519945845,174.64433137453267</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>-38.460891830592466,174.6443375862586</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>-38.46018989192286,174.64425238248123</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>-38.45948824141873,174.6441518298628</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>-38.458786676437015,174.6440464677354</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>-38.45808489532608,174.64392531181554</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>-38.4573789871071,174.64389462135696</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>-38.45667253439785,174.64386568282436</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>-38.455975918464894,174.6437228420357</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>-38.45527767569915,174.6436053563955</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>-38.454575172085036,174.64355445295698</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>-38.453875551109036,174.64345832480487</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>-38.45317376795923,174.64339085853703</t>
+        </is>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>-38.452478570188596,174.64325395147358</t>
+        </is>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>-38.45176690377184,174.64315085510123</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>-38.451059585481204,174.64303584612273</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0259/nzd0259.xlsx
+++ b/data/nzd0259/nzd0259.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U344"/>
+  <dimension ref="A1:U345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24136,6 +24136,75 @@
         <v>326.75</v>
       </c>
       <c r="U344" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>351.03</v>
+      </c>
+      <c r="C345" t="n">
+        <v>331.62</v>
+      </c>
+      <c r="D345" t="n">
+        <v>323.18</v>
+      </c>
+      <c r="E345" t="n">
+        <v>313.33</v>
+      </c>
+      <c r="F345" t="n">
+        <v>314.85</v>
+      </c>
+      <c r="G345" t="n">
+        <v>319.35</v>
+      </c>
+      <c r="H345" t="n">
+        <v>325.97</v>
+      </c>
+      <c r="I345" t="n">
+        <v>334.41</v>
+      </c>
+      <c r="J345" t="n">
+        <v>344.51</v>
+      </c>
+      <c r="K345" t="n">
+        <v>346.5</v>
+      </c>
+      <c r="L345" t="n">
+        <v>345.06</v>
+      </c>
+      <c r="M345" t="n">
+        <v>348.34</v>
+      </c>
+      <c r="N345" t="n">
+        <v>355.18</v>
+      </c>
+      <c r="O345" t="n">
+        <v>353.83</v>
+      </c>
+      <c r="P345" t="n">
+        <v>355.36</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>355.84</v>
+      </c>
+      <c r="R345" t="n">
+        <v>350.23</v>
+      </c>
+      <c r="S345" t="n">
+        <v>340.31</v>
+      </c>
+      <c r="T345" t="n">
+        <v>337.32</v>
+      </c>
+      <c r="U345" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -24152,7 +24221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B352"/>
+  <dimension ref="A1:B353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27675,6 +27744,16 @@
       </c>
       <c r="B352" t="n">
         <v>-0.5</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>-0.39</v>
       </c>
     </row>
   </sheetData>
@@ -27843,28 +27922,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08545956527472678</v>
+        <v>-0.08244997340412309</v>
       </c>
       <c r="J2" t="n">
+        <v>344</v>
+      </c>
+      <c r="K2" t="n">
         <v>343</v>
       </c>
-      <c r="K2" t="n">
-        <v>342</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0120052091803633</v>
+        <v>0.01121440609516933</v>
       </c>
       <c r="M2" t="n">
-        <v>3.944490572294025</v>
+        <v>3.949765757889882</v>
       </c>
       <c r="N2" t="n">
-        <v>32.9441674042267</v>
+        <v>32.93831145456669</v>
       </c>
       <c r="O2" t="n">
-        <v>5.739700985611245</v>
+        <v>5.739190836221312</v>
       </c>
       <c r="P2" t="n">
-        <v>347.6824666561936</v>
+        <v>347.6505446408635</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -27925,28 +28004,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06782025160708832</v>
+        <v>-0.06200876632105024</v>
       </c>
       <c r="J3" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K3" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009704690969654206</v>
+        <v>0.008065513482144238</v>
       </c>
       <c r="M3" t="n">
-        <v>4.141620676153729</v>
+        <v>4.165099699197794</v>
       </c>
       <c r="N3" t="n">
-        <v>25.71773852738018</v>
+        <v>25.9786969761624</v>
       </c>
       <c r="O3" t="n">
-        <v>5.071265968905613</v>
+        <v>5.09693015217615</v>
       </c>
       <c r="P3" t="n">
-        <v>322.6043677640329</v>
+        <v>322.542772569765</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -28007,28 +28086,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.02101719440831298</v>
+        <v>-0.009933037459176628</v>
       </c>
       <c r="J4" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K4" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004591758975710514</v>
+        <v>0.0001008236557442643</v>
       </c>
       <c r="M4" t="n">
-        <v>5.845192871614852</v>
+        <v>5.888839733794205</v>
       </c>
       <c r="N4" t="n">
-        <v>52.68681042964916</v>
+        <v>53.75490897592833</v>
       </c>
       <c r="O4" t="n">
-        <v>7.258568070194642</v>
+        <v>7.33177393104345</v>
       </c>
       <c r="P4" t="n">
-        <v>303.1469502503576</v>
+        <v>303.0294706789616</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -28089,28 +28168,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2466905432027668</v>
+        <v>0.2505892545918607</v>
       </c>
       <c r="J5" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K5" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06948782411829912</v>
+        <v>0.07168436558052393</v>
       </c>
       <c r="M5" t="n">
-        <v>4.728876427466006</v>
+        <v>4.736159805666348</v>
       </c>
       <c r="N5" t="n">
-        <v>44.65286426959975</v>
+        <v>44.67415238791253</v>
       </c>
       <c r="O5" t="n">
-        <v>6.682279870642934</v>
+        <v>6.683872559221378</v>
       </c>
       <c r="P5" t="n">
-        <v>299.6357960882534</v>
+        <v>299.5944741415245</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -28171,28 +28250,28 @@
         <v>0.1324</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3504378619779697</v>
+        <v>0.3594593296909044</v>
       </c>
       <c r="J6" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K6" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04199354086384322</v>
+        <v>0.044097396263306</v>
       </c>
       <c r="M6" t="n">
-        <v>9.93209287137519</v>
+        <v>9.943484500934062</v>
       </c>
       <c r="N6" t="n">
-        <v>152.039574305067</v>
+        <v>152.3943355700901</v>
       </c>
       <c r="O6" t="n">
-        <v>12.33043285148851</v>
+        <v>12.34481006618126</v>
       </c>
       <c r="P6" t="n">
-        <v>289.0858521613936</v>
+        <v>288.9893875064055</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28249,28 +28328,28 @@
         <v>0.1253</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3761042442912775</v>
+        <v>0.3796104252568468</v>
       </c>
       <c r="J7" t="n">
+        <v>344</v>
+      </c>
+      <c r="K7" t="n">
         <v>343</v>
       </c>
-      <c r="K7" t="n">
-        <v>342</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1069029229543783</v>
+        <v>0.1090378811300196</v>
       </c>
       <c r="M7" t="n">
-        <v>5.812592773576632</v>
+        <v>5.813704073839626</v>
       </c>
       <c r="N7" t="n">
-        <v>64.81961172357772</v>
+        <v>64.75314504345198</v>
       </c>
       <c r="O7" t="n">
-        <v>8.051062769819753</v>
+        <v>8.046933890833948</v>
       </c>
       <c r="P7" t="n">
-        <v>303.0005874742016</v>
+        <v>302.96341664598</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28327,28 +28406,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2315577061802985</v>
+        <v>0.2355255657319043</v>
       </c>
       <c r="J8" t="n">
+        <v>344</v>
+      </c>
+      <c r="K8" t="n">
         <v>343</v>
       </c>
-      <c r="K8" t="n">
-        <v>342</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.05492613930970081</v>
+        <v>0.0568454608086314</v>
       </c>
       <c r="M8" t="n">
-        <v>5.439056183079231</v>
+        <v>5.442878978032896</v>
       </c>
       <c r="N8" t="n">
-        <v>50.56819002980505</v>
+        <v>50.57753036650436</v>
       </c>
       <c r="O8" t="n">
-        <v>7.111131416997231</v>
+        <v>7.111788127222601</v>
       </c>
       <c r="P8" t="n">
-        <v>312.5498035963627</v>
+        <v>312.5077174667875</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28405,28 +28484,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2717809445742567</v>
+        <v>0.277655456151966</v>
       </c>
       <c r="J9" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K9" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04599660531774408</v>
+        <v>0.04797318990483268</v>
       </c>
       <c r="M9" t="n">
-        <v>6.884348511476605</v>
+        <v>6.893758882714558</v>
       </c>
       <c r="N9" t="n">
-        <v>84.31057984354857</v>
+        <v>84.40936321040846</v>
       </c>
       <c r="O9" t="n">
-        <v>9.182079276697003</v>
+        <v>9.187456841281403</v>
       </c>
       <c r="P9" t="n">
-        <v>316.3891223985189</v>
+        <v>316.3268733619137</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28483,28 +28562,28 @@
         <v>0.1406</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4907592853809884</v>
+        <v>0.4967696106388156</v>
       </c>
       <c r="J10" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K10" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L10" t="n">
-        <v>0.163267810084379</v>
+        <v>0.1666513295089155</v>
       </c>
       <c r="M10" t="n">
-        <v>6.39121904280919</v>
+        <v>6.403645951942564</v>
       </c>
       <c r="N10" t="n">
-        <v>66.90575921854065</v>
+        <v>67.06360372307219</v>
       </c>
       <c r="O10" t="n">
-        <v>8.179594074191009</v>
+        <v>8.189237065995354</v>
       </c>
       <c r="P10" t="n">
-        <v>320.6366786928298</v>
+        <v>320.5723280888685</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28561,28 +28640,28 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.342399445448184</v>
+        <v>0.3459614524055782</v>
       </c>
       <c r="J11" t="n">
+        <v>344</v>
+      </c>
+      <c r="K11" t="n">
         <v>343</v>
       </c>
-      <c r="K11" t="n">
-        <v>342</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.07876589377656418</v>
+        <v>0.08056340509002347</v>
       </c>
       <c r="M11" t="n">
-        <v>6.229335064339679</v>
+        <v>6.229226961765806</v>
       </c>
       <c r="N11" t="n">
-        <v>75.28775575922138</v>
+        <v>75.19482160459491</v>
       </c>
       <c r="O11" t="n">
-        <v>8.676851719328928</v>
+        <v>8.671494773370673</v>
       </c>
       <c r="P11" t="n">
-        <v>330.9182180225387</v>
+        <v>330.8804845146296</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28639,28 +28718,28 @@
         <v>0.1507</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3795795779237445</v>
+        <v>0.3820529571259547</v>
       </c>
       <c r="J12" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K12" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L12" t="n">
-        <v>0.09170981231318687</v>
+        <v>0.09319672611724417</v>
       </c>
       <c r="M12" t="n">
-        <v>6.868459912218909</v>
+        <v>6.861810714513971</v>
       </c>
       <c r="N12" t="n">
-        <v>78.18896546062626</v>
+        <v>78.02248313971766</v>
       </c>
       <c r="O12" t="n">
-        <v>8.842452457357419</v>
+        <v>8.833033631755155</v>
       </c>
       <c r="P12" t="n">
-        <v>330.5281532749108</v>
+        <v>330.5019382429595</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28717,28 +28796,28 @@
         <v>0.1363</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2566243008071205</v>
+        <v>0.2609202738564002</v>
       </c>
       <c r="J13" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K13" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03941349748793255</v>
+        <v>0.04082513793180087</v>
       </c>
       <c r="M13" t="n">
-        <v>7.714522534602152</v>
+        <v>7.714553204866675</v>
       </c>
       <c r="N13" t="n">
-        <v>86.65846778125146</v>
+        <v>86.58500849926671</v>
       </c>
       <c r="O13" t="n">
-        <v>9.309053001312833</v>
+        <v>9.305106581832725</v>
       </c>
       <c r="P13" t="n">
-        <v>333.7443189795406</v>
+        <v>333.6982826856236</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28795,28 +28874,28 @@
         <v>0.0713</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4843447243181391</v>
+        <v>0.4883165713279915</v>
       </c>
       <c r="J14" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K14" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1370499712029353</v>
+        <v>0.1394210324080448</v>
       </c>
       <c r="M14" t="n">
-        <v>7.150088511206508</v>
+        <v>7.149708886648184</v>
       </c>
       <c r="N14" t="n">
-        <v>80.93694692787739</v>
+        <v>80.85847991269898</v>
       </c>
       <c r="O14" t="n">
-        <v>8.996496369580626</v>
+        <v>8.992134335779186</v>
       </c>
       <c r="P14" t="n">
-        <v>335.1246583638252</v>
+        <v>335.0825612619428</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28873,28 +28952,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4321075049506231</v>
+        <v>0.4346873688103744</v>
       </c>
       <c r="J15" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K15" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1062273521579521</v>
+        <v>0.1078181847135975</v>
       </c>
       <c r="M15" t="n">
-        <v>7.259540750049927</v>
+        <v>7.25165539296676</v>
       </c>
       <c r="N15" t="n">
-        <v>86.08060170596436</v>
+        <v>85.89652741789271</v>
       </c>
       <c r="O15" t="n">
-        <v>9.277963230470595</v>
+        <v>9.268037948664901</v>
       </c>
       <c r="P15" t="n">
-        <v>337.7304153457619</v>
+        <v>337.7030716964528</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28951,28 +29030,28 @@
         <v>0.079</v>
       </c>
       <c r="I16" t="n">
-        <v>0.258068401787076</v>
+        <v>0.2610341677659286</v>
       </c>
       <c r="J16" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K16" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L16" t="n">
-        <v>0.03355505814786264</v>
+        <v>0.03445941095752902</v>
       </c>
       <c r="M16" t="n">
-        <v>8.202551563765011</v>
+        <v>8.194941649932057</v>
       </c>
       <c r="N16" t="n">
-        <v>105.1041242951151</v>
+        <v>104.886022135233</v>
       </c>
       <c r="O16" t="n">
-        <v>10.25203025235075</v>
+        <v>10.2413877055423</v>
       </c>
       <c r="P16" t="n">
-        <v>343.1001846975842</v>
+        <v>343.068750920739</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29029,28 +29108,28 @@
         <v>0.1836</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3432626967543133</v>
+        <v>0.3460535470310454</v>
       </c>
       <c r="J17" t="n">
+        <v>344</v>
+      </c>
+      <c r="K17" t="n">
         <v>343</v>
       </c>
-      <c r="K17" t="n">
-        <v>342</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.04239429329883215</v>
+        <v>0.04326191365904641</v>
       </c>
       <c r="M17" t="n">
-        <v>9.973840995658644</v>
+        <v>9.96057073862077</v>
       </c>
       <c r="N17" t="n">
-        <v>146.1365967155019</v>
+        <v>145.7882374184631</v>
       </c>
       <c r="O17" t="n">
-        <v>12.08869706442766</v>
+        <v>12.07427999586158</v>
       </c>
       <c r="P17" t="n">
-        <v>341.6689036126467</v>
+        <v>341.6393392203672</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29107,28 +29186,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4756390806490796</v>
+        <v>0.4765095865279</v>
       </c>
       <c r="J18" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K18" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L18" t="n">
-        <v>0.06465618263954986</v>
+        <v>0.06521488975533096</v>
       </c>
       <c r="M18" t="n">
-        <v>10.06651724543636</v>
+        <v>10.04121362134005</v>
       </c>
       <c r="N18" t="n">
-        <v>171.7942118927017</v>
+        <v>171.2930645021866</v>
       </c>
       <c r="O18" t="n">
-        <v>13.10702910245879</v>
+        <v>13.0878976349216</v>
       </c>
       <c r="P18" t="n">
-        <v>336.2272361183441</v>
+        <v>336.2177135020605</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -29189,28 +29268,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.674300704836474</v>
+        <v>1.680177502936534</v>
       </c>
       <c r="J19" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K19" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1379129515961157</v>
+        <v>0.1393634897526179</v>
       </c>
       <c r="M19" t="n">
-        <v>26.6221175845404</v>
+        <v>26.56725125463869</v>
       </c>
       <c r="N19" t="n">
-        <v>951.4191653511458</v>
+        <v>948.9535807408581</v>
       </c>
       <c r="O19" t="n">
-        <v>30.84508332540448</v>
+        <v>30.80509017582741</v>
       </c>
       <c r="P19" t="n">
-        <v>285.6926944873234</v>
+        <v>285.629752351968</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -29271,28 +29350,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9031352821573018</v>
+        <v>0.9177853265093916</v>
       </c>
       <c r="J20" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K20" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05361789766049507</v>
+        <v>0.05542180476530523</v>
       </c>
       <c r="M20" t="n">
-        <v>23.75290191408999</v>
+        <v>23.74903427102211</v>
       </c>
       <c r="N20" t="n">
-        <v>777.4735497453481</v>
+        <v>777.28611928584</v>
       </c>
       <c r="O20" t="n">
-        <v>27.88321268694388</v>
+        <v>27.87985149325297</v>
       </c>
       <c r="P20" t="n">
-        <v>286.8495971286395</v>
+        <v>286.6923199251036</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -29334,7 +29413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U344"/>
+  <dimension ref="A1:U345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66017,6 +66096,113 @@
         </is>
       </c>
     </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>-38.46371383881957,174.6439334260905</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>-38.463006234590026,174.6441443609217</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>-38.462301039293024,174.64422962052515</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>-38.461595526553324,174.64433103085995</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>-38.46089251115378,174.6443021883157</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>-38.460190145196066,174.6442392086167</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>-38.45948823921646,174.64415194441705</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>-38.45878672708641,174.64404383301323</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>-38.4580850903214,174.64391672142466</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>-38.45737988820085,174.64387460172904</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>-38.456674898609286,174.6438286795516</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>-38.45597553173277,174.6437288949827</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>-38.455278755612106,174.64358845398675</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>-38.45457599660798,174.64354154786398</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>-38.453875332211645,174.643461750903</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>-38.45317336379601,174.6433942572492</t>
+        </is>
+      </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>-38.45247484824661,174.6432721362969</t>
+        </is>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>-38.45177091815096,174.64313372571743</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>-38.45108678537771,174.64291978463862</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0259/nzd0259.xlsx
+++ b/data/nzd0259/nzd0259.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U345"/>
+  <dimension ref="A1:U346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24160,7 +24160,7 @@
         <v>313.33</v>
       </c>
       <c r="F345" t="n">
-        <v>314.85</v>
+        <v>311.71</v>
       </c>
       <c r="G345" t="n">
         <v>319.35</v>
@@ -24207,6 +24207,75 @@
       <c r="U345" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>353.63</v>
+      </c>
+      <c r="C346" t="n">
+        <v>331.59</v>
+      </c>
+      <c r="D346" t="n">
+        <v>322.83</v>
+      </c>
+      <c r="E346" t="n">
+        <v>313.92</v>
+      </c>
+      <c r="F346" t="n">
+        <v>316.19</v>
+      </c>
+      <c r="G346" t="n">
+        <v>323.64</v>
+      </c>
+      <c r="H346" t="n">
+        <v>329.53</v>
+      </c>
+      <c r="I346" t="n">
+        <v>337.68</v>
+      </c>
+      <c r="J346" t="n">
+        <v>347.49</v>
+      </c>
+      <c r="K346" t="n">
+        <v>349.71</v>
+      </c>
+      <c r="L346" t="n">
+        <v>347.59</v>
+      </c>
+      <c r="M346" t="n">
+        <v>351.47</v>
+      </c>
+      <c r="N346" t="n">
+        <v>357.74</v>
+      </c>
+      <c r="O346" t="n">
+        <v>356.75</v>
+      </c>
+      <c r="P346" t="n">
+        <v>357.51</v>
+      </c>
+      <c r="Q346" t="n">
+        <v>358.48</v>
+      </c>
+      <c r="R346" t="n">
+        <v>354.29</v>
+      </c>
+      <c r="S346" t="n">
+        <v>343.67</v>
+      </c>
+      <c r="T346" t="n">
+        <v>340.2</v>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -24221,7 +24290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B353"/>
+  <dimension ref="A1:B355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27754,6 +27823,26 @@
       </c>
       <c r="B353" t="n">
         <v>-0.39</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>-0.8</v>
       </c>
     </row>
   </sheetData>
@@ -27922,28 +28011,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08244997340412309</v>
+        <v>-0.07803065741156012</v>
       </c>
       <c r="J2" t="n">
+        <v>345</v>
+      </c>
+      <c r="K2" t="n">
         <v>344</v>
       </c>
-      <c r="K2" t="n">
-        <v>343</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.01121440609516933</v>
+        <v>0.01005417590317281</v>
       </c>
       <c r="M2" t="n">
-        <v>3.949765757889882</v>
+        <v>3.962497757957007</v>
       </c>
       <c r="N2" t="n">
-        <v>32.93831145456669</v>
+        <v>33.03395884389482</v>
       </c>
       <c r="O2" t="n">
-        <v>5.739190836221312</v>
+        <v>5.747517624496233</v>
       </c>
       <c r="P2" t="n">
-        <v>347.6505446408635</v>
+        <v>347.6033144195741</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -28004,28 +28093,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06200876632105024</v>
+        <v>-0.05622120062381775</v>
       </c>
       <c r="J3" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K3" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008065513482144238</v>
+        <v>0.006593987905301635</v>
       </c>
       <c r="M3" t="n">
-        <v>4.165099699197794</v>
+        <v>4.188165450075057</v>
       </c>
       <c r="N3" t="n">
-        <v>25.9786969761624</v>
+        <v>26.23111558083268</v>
       </c>
       <c r="O3" t="n">
-        <v>5.09693015217615</v>
+        <v>5.121632120802184</v>
       </c>
       <c r="P3" t="n">
-        <v>322.542772569765</v>
+        <v>322.4809671921464</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -28086,28 +28175,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.009933037459176628</v>
+        <v>0.0009429636678294352</v>
       </c>
       <c r="J4" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K4" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001008236557442643</v>
+        <v>8.945250369318813e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>5.888839733794205</v>
+        <v>5.933460904669669</v>
       </c>
       <c r="N4" t="n">
-        <v>53.75490897592833</v>
+        <v>54.75640436237371</v>
       </c>
       <c r="O4" t="n">
-        <v>7.33177393104345</v>
+        <v>7.399757047523501</v>
       </c>
       <c r="P4" t="n">
-        <v>303.0294706789616</v>
+        <v>302.9133259314461</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -28168,28 +28257,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2505892545918607</v>
+        <v>0.254779369449423</v>
       </c>
       <c r="J5" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K5" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07168436558052393</v>
+        <v>0.07404395051821921</v>
       </c>
       <c r="M5" t="n">
-        <v>4.736159805666348</v>
+        <v>4.744639366668796</v>
       </c>
       <c r="N5" t="n">
-        <v>44.67415238791253</v>
+        <v>44.71643783642207</v>
       </c>
       <c r="O5" t="n">
-        <v>6.683872559221378</v>
+        <v>6.687035055719543</v>
       </c>
       <c r="P5" t="n">
-        <v>299.5944741415245</v>
+        <v>299.5497279313587</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -28250,28 +28339,28 @@
         <v>0.1324</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3594593296909044</v>
+        <v>0.3674726736167315</v>
       </c>
       <c r="J6" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K6" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L6" t="n">
-        <v>0.044097396263306</v>
+        <v>0.04605586452470289</v>
       </c>
       <c r="M6" t="n">
-        <v>9.943484500934062</v>
+        <v>9.949637023251407</v>
       </c>
       <c r="N6" t="n">
-        <v>152.3943355700901</v>
+        <v>152.5898682052721</v>
       </c>
       <c r="O6" t="n">
-        <v>12.34481006618126</v>
+        <v>12.3527271565947</v>
       </c>
       <c r="P6" t="n">
-        <v>288.9893875064055</v>
+        <v>288.9029175201811</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28328,28 +28417,28 @@
         <v>0.1253</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3796104252568468</v>
+        <v>0.3854033970929546</v>
       </c>
       <c r="J7" t="n">
+        <v>345</v>
+      </c>
+      <c r="K7" t="n">
         <v>344</v>
       </c>
-      <c r="K7" t="n">
-        <v>343</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1090378811300196</v>
+        <v>0.1120674000079105</v>
       </c>
       <c r="M7" t="n">
-        <v>5.813704073839626</v>
+        <v>5.826779630484246</v>
       </c>
       <c r="N7" t="n">
-        <v>64.75314504345198</v>
+        <v>64.89405950154647</v>
       </c>
       <c r="O7" t="n">
-        <v>8.046933890833948</v>
+        <v>8.05568491821437</v>
       </c>
       <c r="P7" t="n">
-        <v>302.96341664598</v>
+        <v>302.9015361798495</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28406,28 +28495,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2355255657319043</v>
+        <v>0.2413929788196199</v>
       </c>
       <c r="J8" t="n">
+        <v>345</v>
+      </c>
+      <c r="K8" t="n">
         <v>344</v>
       </c>
-      <c r="K8" t="n">
-        <v>343</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.0568454608086314</v>
+        <v>0.05948288830492876</v>
       </c>
       <c r="M8" t="n">
-        <v>5.442878978032896</v>
+        <v>5.455626294418996</v>
       </c>
       <c r="N8" t="n">
-        <v>50.57753036650436</v>
+        <v>50.7678841759875</v>
       </c>
       <c r="O8" t="n">
-        <v>7.111788127222601</v>
+        <v>7.125158536902004</v>
       </c>
       <c r="P8" t="n">
-        <v>312.5077174667875</v>
+        <v>312.4450111070261</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28484,28 +28573,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.277655456151966</v>
+        <v>0.2852667954763571</v>
       </c>
       <c r="J9" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K9" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04797318990483268</v>
+        <v>0.05044825995254443</v>
       </c>
       <c r="M9" t="n">
-        <v>6.893758882714558</v>
+        <v>6.911283320709377</v>
       </c>
       <c r="N9" t="n">
-        <v>84.40936321040846</v>
+        <v>84.73420419663005</v>
       </c>
       <c r="O9" t="n">
-        <v>9.187456841281403</v>
+        <v>9.205118369506719</v>
       </c>
       <c r="P9" t="n">
-        <v>316.3268733619137</v>
+        <v>316.2456022494346</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28562,28 +28651,28 @@
         <v>0.1406</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4967696106388156</v>
+        <v>0.5043600918436195</v>
       </c>
       <c r="J10" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K10" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1666513295089155</v>
+        <v>0.1705288471003863</v>
       </c>
       <c r="M10" t="n">
-        <v>6.403645951942564</v>
+        <v>6.424703672783066</v>
       </c>
       <c r="N10" t="n">
-        <v>67.06360372307219</v>
+        <v>67.42349310073206</v>
       </c>
       <c r="O10" t="n">
-        <v>8.189237065995354</v>
+        <v>8.211180980877968</v>
       </c>
       <c r="P10" t="n">
-        <v>320.5723280888685</v>
+        <v>320.4904450543804</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28640,28 +28729,28 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3459614524055782</v>
+        <v>0.3512288018051783</v>
       </c>
       <c r="J11" t="n">
+        <v>345</v>
+      </c>
+      <c r="K11" t="n">
         <v>344</v>
       </c>
-      <c r="K11" t="n">
-        <v>343</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.08056340509002347</v>
+        <v>0.08298107735650195</v>
       </c>
       <c r="M11" t="n">
-        <v>6.229226961765806</v>
+        <v>6.237950943315592</v>
       </c>
       <c r="N11" t="n">
-        <v>75.19482160459491</v>
+        <v>75.24862353363149</v>
       </c>
       <c r="O11" t="n">
-        <v>8.671494773370673</v>
+        <v>8.674596447883411</v>
       </c>
       <c r="P11" t="n">
-        <v>330.8804845146296</v>
+        <v>330.8242618940527</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28718,28 +28807,28 @@
         <v>0.1507</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3820529571259547</v>
+        <v>0.3858649632916912</v>
       </c>
       <c r="J12" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K12" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L12" t="n">
-        <v>0.09319672611724417</v>
+        <v>0.09521431338715702</v>
       </c>
       <c r="M12" t="n">
-        <v>6.861810714513971</v>
+        <v>6.862118016464189</v>
       </c>
       <c r="N12" t="n">
-        <v>78.02248313971766</v>
+        <v>77.93850403009795</v>
       </c>
       <c r="O12" t="n">
-        <v>8.833033631755155</v>
+        <v>8.828278656119659</v>
       </c>
       <c r="P12" t="n">
-        <v>330.5019382429595</v>
+        <v>330.4612298531316</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28796,28 +28885,28 @@
         <v>0.1363</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2609202738564002</v>
+        <v>0.2669038629309323</v>
       </c>
       <c r="J13" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K13" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04082513793180087</v>
+        <v>0.04270655790406108</v>
       </c>
       <c r="M13" t="n">
-        <v>7.714553204866675</v>
+        <v>7.723310890295217</v>
       </c>
       <c r="N13" t="n">
-        <v>86.58500849926671</v>
+        <v>86.67608004925667</v>
       </c>
       <c r="O13" t="n">
-        <v>9.305106581832725</v>
+        <v>9.309998928531446</v>
       </c>
       <c r="P13" t="n">
-        <v>333.6982826856236</v>
+        <v>333.6336817087202</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28874,28 +28963,28 @@
         <v>0.0713</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4883165713279915</v>
+        <v>0.4936280166982027</v>
       </c>
       <c r="J14" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K14" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1394210324080448</v>
+        <v>0.1423052875806812</v>
       </c>
       <c r="M14" t="n">
-        <v>7.149708886648184</v>
+        <v>7.155768337459778</v>
       </c>
       <c r="N14" t="n">
-        <v>80.85847991269898</v>
+        <v>80.90012424821776</v>
       </c>
       <c r="O14" t="n">
-        <v>8.992134335779186</v>
+        <v>8.994449635648518</v>
       </c>
       <c r="P14" t="n">
-        <v>335.0825612619428</v>
+        <v>335.0258403702969</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28952,28 +29041,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4346873688103744</v>
+        <v>0.4388079810034121</v>
       </c>
       <c r="J15" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K15" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1078181847135975</v>
+        <v>0.1100062535089104</v>
       </c>
       <c r="M15" t="n">
-        <v>7.25165539296676</v>
+        <v>7.251531848289078</v>
       </c>
       <c r="N15" t="n">
-        <v>85.89652741789271</v>
+        <v>85.81367639410233</v>
       </c>
       <c r="O15" t="n">
-        <v>9.268037948664901</v>
+        <v>9.26356715278204</v>
       </c>
       <c r="P15" t="n">
-        <v>337.7030716964528</v>
+        <v>337.6590677048035</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29030,28 +29119,28 @@
         <v>0.079</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2610341677659286</v>
+        <v>0.265137771800221</v>
       </c>
       <c r="J16" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K16" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L16" t="n">
-        <v>0.03445941095752902</v>
+        <v>0.03565123855925068</v>
       </c>
       <c r="M16" t="n">
-        <v>8.194941649932057</v>
+        <v>8.193229944697212</v>
       </c>
       <c r="N16" t="n">
-        <v>104.886022135233</v>
+        <v>104.7467605441843</v>
       </c>
       <c r="O16" t="n">
-        <v>10.2413877055423</v>
+        <v>10.23458648623306</v>
       </c>
       <c r="P16" t="n">
-        <v>343.068750920739</v>
+        <v>343.0249285591098</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29108,28 +29197,28 @@
         <v>0.1836</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3460535470310454</v>
+        <v>0.3502412756685125</v>
       </c>
       <c r="J17" t="n">
+        <v>345</v>
+      </c>
+      <c r="K17" t="n">
         <v>344</v>
       </c>
-      <c r="K17" t="n">
-        <v>343</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.04326191365904641</v>
+        <v>0.04445617578384298</v>
       </c>
       <c r="M17" t="n">
-        <v>9.96057073862077</v>
+        <v>9.954994941299528</v>
       </c>
       <c r="N17" t="n">
-        <v>145.7882374184631</v>
+        <v>145.5366079402746</v>
       </c>
       <c r="O17" t="n">
-        <v>12.07427999586158</v>
+        <v>12.06385543432424</v>
       </c>
       <c r="P17" t="n">
-        <v>341.6393392203672</v>
+        <v>341.5946402531255</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29186,28 +29275,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4765095865279</v>
+        <v>0.4796165015591379</v>
       </c>
       <c r="J18" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K18" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L18" t="n">
-        <v>0.06521488975533096</v>
+        <v>0.06633131531132852</v>
       </c>
       <c r="M18" t="n">
-        <v>10.04121362134005</v>
+        <v>10.02727864737344</v>
       </c>
       <c r="N18" t="n">
-        <v>171.2930645021866</v>
+        <v>170.8769938267658</v>
       </c>
       <c r="O18" t="n">
-        <v>13.0878976349216</v>
+        <v>13.07199272592996</v>
       </c>
       <c r="P18" t="n">
-        <v>336.2177135020605</v>
+        <v>336.1834765232899</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -29268,28 +29357,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.680177502936534</v>
+        <v>1.68774139631237</v>
       </c>
       <c r="J19" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K19" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1393634897526179</v>
+        <v>0.1410510929325161</v>
       </c>
       <c r="M19" t="n">
-        <v>26.56725125463869</v>
+        <v>26.51893031904152</v>
       </c>
       <c r="N19" t="n">
-        <v>948.9535807408581</v>
+        <v>946.7182668259383</v>
       </c>
       <c r="O19" t="n">
-        <v>30.80509017582741</v>
+        <v>30.76878721733988</v>
       </c>
       <c r="P19" t="n">
-        <v>285.629752351968</v>
+        <v>285.5481246544383</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -29350,28 +29439,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9177853265093916</v>
+        <v>0.9339140365734951</v>
       </c>
       <c r="J20" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K20" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05542180476530523</v>
+        <v>0.05740400453624839</v>
       </c>
       <c r="M20" t="n">
-        <v>23.74903427102211</v>
+        <v>23.7505370139644</v>
       </c>
       <c r="N20" t="n">
-        <v>777.28611928584</v>
+        <v>777.5102481733971</v>
       </c>
       <c r="O20" t="n">
-        <v>27.87985149325297</v>
+        <v>27.88387075306076</v>
       </c>
       <c r="P20" t="n">
-        <v>286.6923199251036</v>
+        <v>286.5178631689244</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -29413,7 +29502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U345"/>
+  <dimension ref="A1:U346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66124,7 +66213,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>-38.46089251115378,174.6443021883157</t>
+          <t>-38.46089181958005,174.6443381590408</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -66200,6 +66289,113 @@
       <c r="U345" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>-38.463714411374646,174.6439036402462</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>-38.46300622798299,174.6441447046011</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>-38.46230096220871,174.64423363007907</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>-38.461595656500066,174.64432427196382</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>-38.46089280628061,174.64428683775114</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>-38.46019109000215,174.64419006437296</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>-38.45948902321685,174.6441111631069</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>-38.45878744718242,174.64400637413667</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>-38.45808586509658,174.64388258893754</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>-38.45738154105536,174.64383788000993</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>-38.456676744729265,174.64379978501879</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>-38.4559778156369,174.6436931483323</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>-38.455280623563915,174.64355921738644</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>-38.454578127227116,174.64350820018842</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>-38.453876900974045,174.64343719719932</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>-38.45317692042892,174.6433643485805</t>
+        </is>
+      </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>-38.45248406231739,174.64322711776728</t>
+        </is>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>-38.451779564497635,174.64309683165337</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>-38.45109419649356,174.64288816143704</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0259/nzd0259.xlsx
+++ b/data/nzd0259/nzd0259.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U346"/>
+  <dimension ref="A1:U348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24276,6 +24276,144 @@
       <c r="U346" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>353.45</v>
+      </c>
+      <c r="C347" t="n">
+        <v>330.17</v>
+      </c>
+      <c r="D347" t="n">
+        <v>320.86</v>
+      </c>
+      <c r="E347" t="n">
+        <v>313.32</v>
+      </c>
+      <c r="F347" t="n">
+        <v>315.74</v>
+      </c>
+      <c r="G347" t="n">
+        <v>322.32</v>
+      </c>
+      <c r="H347" t="n">
+        <v>329.36</v>
+      </c>
+      <c r="I347" t="n">
+        <v>336.74</v>
+      </c>
+      <c r="J347" t="n">
+        <v>346.13</v>
+      </c>
+      <c r="K347" t="n">
+        <v>349.25</v>
+      </c>
+      <c r="L347" t="n">
+        <v>347.09</v>
+      </c>
+      <c r="M347" t="n">
+        <v>350.71</v>
+      </c>
+      <c r="N347" t="n">
+        <v>357.91</v>
+      </c>
+      <c r="O347" t="n">
+        <v>355.96</v>
+      </c>
+      <c r="P347" t="n">
+        <v>357.54</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>358.27</v>
+      </c>
+      <c r="R347" t="n">
+        <v>354.42</v>
+      </c>
+      <c r="S347" t="n">
+        <v>344.42</v>
+      </c>
+      <c r="T347" t="n">
+        <v>333.42</v>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>352.33</v>
+      </c>
+      <c r="C348" t="n">
+        <v>327.91</v>
+      </c>
+      <c r="D348" t="n">
+        <v>317.36</v>
+      </c>
+      <c r="E348" t="n">
+        <v>310.98</v>
+      </c>
+      <c r="F348" t="n">
+        <v>313.77</v>
+      </c>
+      <c r="G348" t="n">
+        <v>323.2</v>
+      </c>
+      <c r="H348" t="n">
+        <v>327.92</v>
+      </c>
+      <c r="I348" t="n">
+        <v>335.37</v>
+      </c>
+      <c r="J348" t="n">
+        <v>345.5</v>
+      </c>
+      <c r="K348" t="n">
+        <v>350.86</v>
+      </c>
+      <c r="L348" t="n">
+        <v>349.61</v>
+      </c>
+      <c r="M348" t="n">
+        <v>351.63</v>
+      </c>
+      <c r="N348" t="n">
+        <v>360.97</v>
+      </c>
+      <c r="O348" t="n">
+        <v>357.24</v>
+      </c>
+      <c r="P348" t="n">
+        <v>359.31</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>362.85</v>
+      </c>
+      <c r="R348" t="n">
+        <v>357.69</v>
+      </c>
+      <c r="S348" t="n">
+        <v>347.98</v>
+      </c>
+      <c r="T348" t="n">
+        <v>329.08</v>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -24290,7 +24428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B355"/>
+  <dimension ref="A1:B357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27843,6 +27981,26 @@
       </c>
       <c r="B355" t="n">
         <v>-0.8</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>1.64</v>
       </c>
     </row>
   </sheetData>
@@ -28011,28 +28169,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07803065741156012</v>
+        <v>-0.07016659695547722</v>
       </c>
       <c r="J2" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K2" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01005417590317281</v>
+        <v>0.008159764386490798</v>
       </c>
       <c r="M2" t="n">
-        <v>3.962497757957007</v>
+        <v>3.982483873651876</v>
       </c>
       <c r="N2" t="n">
-        <v>33.03395884389482</v>
+        <v>33.15132811366412</v>
       </c>
       <c r="O2" t="n">
-        <v>5.747517624496233</v>
+        <v>5.757719002666257</v>
       </c>
       <c r="P2" t="n">
-        <v>347.6033144195741</v>
+        <v>347.519097440456</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -28093,28 +28251,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05622120062381775</v>
+        <v>-0.04761582030446946</v>
       </c>
       <c r="J3" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K3" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006593987905301635</v>
+        <v>0.004724119283816552</v>
       </c>
       <c r="M3" t="n">
-        <v>4.188165450075057</v>
+        <v>4.21584173003803</v>
       </c>
       <c r="N3" t="n">
-        <v>26.23111558083268</v>
+        <v>26.45377957909156</v>
       </c>
       <c r="O3" t="n">
-        <v>5.121632120802184</v>
+        <v>5.143323787113889</v>
       </c>
       <c r="P3" t="n">
-        <v>322.4809671921464</v>
+        <v>322.3888893127286</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -28175,28 +28333,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0009429636678294352</v>
+        <v>0.01824731249101736</v>
       </c>
       <c r="J4" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K4" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L4" t="n">
-        <v>8.945250369318813e-07</v>
+        <v>0.0003295272489654</v>
       </c>
       <c r="M4" t="n">
-        <v>5.933460904669669</v>
+        <v>6.000445878059021</v>
       </c>
       <c r="N4" t="n">
-        <v>54.75640436237371</v>
+        <v>55.94044486380398</v>
       </c>
       <c r="O4" t="n">
-        <v>7.399757047523501</v>
+        <v>7.479334520116344</v>
       </c>
       <c r="P4" t="n">
-        <v>302.9133259314461</v>
+        <v>302.7281624765465</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -28257,28 +28415,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.254779369449423</v>
+        <v>0.2610715695242858</v>
       </c>
       <c r="J5" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K5" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07404395051821921</v>
+        <v>0.0779292825061243</v>
       </c>
       <c r="M5" t="n">
-        <v>4.744639366668796</v>
+        <v>4.750429151043541</v>
       </c>
       <c r="N5" t="n">
-        <v>44.71643783642207</v>
+        <v>44.66273121184792</v>
       </c>
       <c r="O5" t="n">
-        <v>6.687035055719543</v>
+        <v>6.683018121466373</v>
       </c>
       <c r="P5" t="n">
-        <v>299.5497279313587</v>
+        <v>299.4824055226955</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -28339,28 +28497,28 @@
         <v>0.1324</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3674726736167315</v>
+        <v>0.3849399289250754</v>
       </c>
       <c r="J6" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K6" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04605586452470289</v>
+        <v>0.05037535762475209</v>
       </c>
       <c r="M6" t="n">
-        <v>9.949637023251407</v>
+        <v>9.968836013778347</v>
       </c>
       <c r="N6" t="n">
-        <v>152.5898682052721</v>
+        <v>153.2021122302814</v>
       </c>
       <c r="O6" t="n">
-        <v>12.3527271565947</v>
+        <v>12.37748408321665</v>
       </c>
       <c r="P6" t="n">
-        <v>288.9029175201811</v>
+        <v>288.7143469923323</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28417,28 +28575,28 @@
         <v>0.1253</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3854033970929546</v>
+        <v>0.3957854716551596</v>
       </c>
       <c r="J7" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K7" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1120674000079105</v>
+        <v>0.1177635992665437</v>
       </c>
       <c r="M7" t="n">
-        <v>5.826779630484246</v>
+        <v>5.846805338912305</v>
       </c>
       <c r="N7" t="n">
-        <v>64.89405950154647</v>
+        <v>65.05444780930527</v>
       </c>
       <c r="O7" t="n">
-        <v>8.05568491821437</v>
+        <v>8.065633751250132</v>
       </c>
       <c r="P7" t="n">
-        <v>302.9015361798495</v>
+        <v>302.7903934643895</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28495,28 +28653,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2413929788196199</v>
+        <v>0.2519201540886671</v>
       </c>
       <c r="J8" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K8" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05948288830492876</v>
+        <v>0.0644566480286195</v>
       </c>
       <c r="M8" t="n">
-        <v>5.455626294418996</v>
+        <v>5.474836416341284</v>
       </c>
       <c r="N8" t="n">
-        <v>50.7678841759875</v>
+        <v>51.02676397076397</v>
       </c>
       <c r="O8" t="n">
-        <v>7.125158536902004</v>
+        <v>7.143302035526985</v>
       </c>
       <c r="P8" t="n">
-        <v>312.4450111070261</v>
+        <v>312.3322743525106</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28573,28 +28731,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2852667954763571</v>
+        <v>0.2984191501342977</v>
       </c>
       <c r="J9" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K9" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05044825995254443</v>
+        <v>0.05499047877125107</v>
       </c>
       <c r="M9" t="n">
-        <v>6.911283320709377</v>
+        <v>6.936391527416242</v>
       </c>
       <c r="N9" t="n">
-        <v>84.73420419663005</v>
+        <v>85.10755086410836</v>
       </c>
       <c r="O9" t="n">
-        <v>9.205118369506719</v>
+        <v>9.225375377951206</v>
       </c>
       <c r="P9" t="n">
-        <v>316.2456022494346</v>
+        <v>316.1048730531573</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28651,28 +28809,28 @@
         <v>0.1406</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5043600918436195</v>
+        <v>0.5173857110041566</v>
       </c>
       <c r="J10" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K10" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1705288471003863</v>
+        <v>0.1776967788298391</v>
       </c>
       <c r="M10" t="n">
-        <v>6.424703672783066</v>
+        <v>6.460443056171434</v>
       </c>
       <c r="N10" t="n">
-        <v>67.42349310073206</v>
+        <v>67.85971793096314</v>
       </c>
       <c r="O10" t="n">
-        <v>8.211180980877968</v>
+        <v>8.237701010049051</v>
       </c>
       <c r="P10" t="n">
-        <v>320.4904450543804</v>
+        <v>320.3496361100005</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28729,28 +28887,28 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3512288018051783</v>
+        <v>0.3618983129065263</v>
       </c>
       <c r="J11" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K11" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08298107735650195</v>
+        <v>0.08793462647129335</v>
       </c>
       <c r="M11" t="n">
-        <v>6.237950943315592</v>
+        <v>6.255922984997056</v>
       </c>
       <c r="N11" t="n">
-        <v>75.24862353363149</v>
+        <v>75.38219362487634</v>
       </c>
       <c r="O11" t="n">
-        <v>8.674596447883411</v>
+        <v>8.682291956901492</v>
       </c>
       <c r="P11" t="n">
-        <v>330.8242618940527</v>
+        <v>330.7101252035438</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28807,28 +28965,28 @@
         <v>0.1507</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3858649632916912</v>
+        <v>0.3941206554585569</v>
       </c>
       <c r="J12" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K12" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L12" t="n">
-        <v>0.09521431338715702</v>
+        <v>0.09952177013970831</v>
       </c>
       <c r="M12" t="n">
-        <v>6.862118016464189</v>
+        <v>6.866443957855641</v>
       </c>
       <c r="N12" t="n">
-        <v>77.93850403009795</v>
+        <v>77.83520674308484</v>
       </c>
       <c r="O12" t="n">
-        <v>8.828278656119659</v>
+        <v>8.822426352375226</v>
       </c>
       <c r="P12" t="n">
-        <v>330.4612298531316</v>
+        <v>330.3728650598359</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28885,28 +29043,28 @@
         <v>0.1363</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2669038629309323</v>
+        <v>0.2782829815241739</v>
       </c>
       <c r="J13" t="n">
+        <v>347</v>
+      </c>
+      <c r="K13" t="n">
         <v>345</v>
       </c>
-      <c r="K13" t="n">
-        <v>343</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.04270655790406108</v>
+        <v>0.04642649817862543</v>
       </c>
       <c r="M13" t="n">
-        <v>7.723310890295217</v>
+        <v>7.738673340194424</v>
       </c>
       <c r="N13" t="n">
-        <v>86.67608004925667</v>
+        <v>86.80283449825755</v>
       </c>
       <c r="O13" t="n">
-        <v>9.309998928531446</v>
+        <v>9.316803877846606</v>
       </c>
       <c r="P13" t="n">
-        <v>333.6336817087202</v>
+        <v>333.5105650275161</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28963,28 +29121,28 @@
         <v>0.0713</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4936280166982027</v>
+        <v>0.5058304662231815</v>
       </c>
       <c r="J14" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K14" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1423052875806812</v>
+        <v>0.1486059594780673</v>
       </c>
       <c r="M14" t="n">
-        <v>7.155768337459778</v>
+        <v>7.178216106129422</v>
       </c>
       <c r="N14" t="n">
-        <v>80.90012424821776</v>
+        <v>81.18333936492924</v>
       </c>
       <c r="O14" t="n">
-        <v>8.994449635648518</v>
+        <v>9.010179763186152</v>
       </c>
       <c r="P14" t="n">
-        <v>335.0258403702969</v>
+        <v>334.8952354519357</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29041,28 +29199,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4388079810034121</v>
+        <v>0.4466963895285026</v>
       </c>
       <c r="J15" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K15" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1100062535089104</v>
+        <v>0.1143015041767794</v>
       </c>
       <c r="M15" t="n">
-        <v>7.251531848289078</v>
+        <v>7.24969666963799</v>
       </c>
       <c r="N15" t="n">
-        <v>85.81367639410233</v>
+        <v>85.62910618956694</v>
       </c>
       <c r="O15" t="n">
-        <v>9.26356715278204</v>
+        <v>9.253599634173014</v>
       </c>
       <c r="P15" t="n">
-        <v>337.6590677048035</v>
+        <v>337.5746409933211</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29119,28 +29277,28 @@
         <v>0.079</v>
       </c>
       <c r="I16" t="n">
-        <v>0.265137771800221</v>
+        <v>0.2741384168598651</v>
       </c>
       <c r="J16" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K16" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L16" t="n">
-        <v>0.03565123855925068</v>
+        <v>0.03828535641032582</v>
       </c>
       <c r="M16" t="n">
-        <v>8.193229944697212</v>
+        <v>8.193842049827193</v>
       </c>
       <c r="N16" t="n">
-        <v>104.7467605441843</v>
+        <v>104.5480411431469</v>
       </c>
       <c r="O16" t="n">
-        <v>10.23458648623306</v>
+        <v>10.22487364925098</v>
       </c>
       <c r="P16" t="n">
-        <v>343.0249285591098</v>
+        <v>342.9285961089065</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29197,28 +29355,28 @@
         <v>0.1836</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3502412756685125</v>
+        <v>0.360653178311276</v>
       </c>
       <c r="J17" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K17" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04445617578384298</v>
+        <v>0.04733623124259845</v>
       </c>
       <c r="M17" t="n">
-        <v>9.954994941299528</v>
+        <v>9.955393034518965</v>
       </c>
       <c r="N17" t="n">
-        <v>145.5366079402746</v>
+        <v>145.2630330090082</v>
       </c>
       <c r="O17" t="n">
-        <v>12.06385543432424</v>
+        <v>12.05251148138877</v>
       </c>
       <c r="P17" t="n">
-        <v>341.5946402531255</v>
+        <v>341.4832407543956</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29275,28 +29433,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4796165015591379</v>
+        <v>0.4876428563718345</v>
       </c>
       <c r="J18" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K18" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L18" t="n">
-        <v>0.06633131531132852</v>
+        <v>0.06902025027358172</v>
       </c>
       <c r="M18" t="n">
-        <v>10.02727864737344</v>
+        <v>10.00854566791883</v>
       </c>
       <c r="N18" t="n">
-        <v>170.8769938267658</v>
+        <v>170.1910801370067</v>
       </c>
       <c r="O18" t="n">
-        <v>13.07199272592996</v>
+        <v>13.04573034126517</v>
       </c>
       <c r="P18" t="n">
-        <v>336.1834765232899</v>
+        <v>336.0948260398194</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -29357,28 +29515,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.68774139631237</v>
+        <v>1.705211889217473</v>
       </c>
       <c r="J19" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K19" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1410510929325161</v>
+        <v>0.1447371429640548</v>
       </c>
       <c r="M19" t="n">
-        <v>26.51893031904152</v>
+        <v>26.43194032823588</v>
       </c>
       <c r="N19" t="n">
-        <v>946.7182668259383</v>
+        <v>942.6978185837503</v>
       </c>
       <c r="O19" t="n">
-        <v>30.76878721733988</v>
+        <v>30.70338448092897</v>
       </c>
       <c r="P19" t="n">
-        <v>285.5481246544383</v>
+        <v>285.359163041642</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -29439,28 +29597,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9339140365734951</v>
+        <v>0.9557268405987314</v>
       </c>
       <c r="J20" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K20" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05740400453624839</v>
+        <v>0.06041378057544333</v>
       </c>
       <c r="M20" t="n">
-        <v>23.7505370139644</v>
+        <v>23.70869712129472</v>
       </c>
       <c r="N20" t="n">
-        <v>777.5102481733971</v>
+        <v>775.3208981565524</v>
       </c>
       <c r="O20" t="n">
-        <v>27.88387075306076</v>
+        <v>27.84458471869445</v>
       </c>
       <c r="P20" t="n">
-        <v>286.5178631689244</v>
+        <v>286.2814528758184</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -29502,7 +29660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U346"/>
+  <dimension ref="A1:U348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66399,6 +66557,220 @@
         </is>
       </c>
     </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>-38.46371437173646,174.64390570234315</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>-38.46300591524959,174.64416097209332</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>-38.46230052833153,174.64425619813954</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>-38.46159552435083,174.64433114541754</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>-38.46089270717108,174.6442919927915</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>-38.46019079929478,174.64420518567894</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>-38.45948898577894,174.64411311052908</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>-38.458787240183554,174.6440171421319</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>-38.45808551150913,174.64389816618012</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>-38.45738130419842,174.64384314231248</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>-38.45667637988398,174.64380549540093</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>-38.45597726107972,174.6437018280304</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>-38.45528074760733,174.6435572758934</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>-38.45457755079342,174.64351722233374</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>-38.453876922863714,174.64343685458948</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>-38.45317663751522,174.64336672767925</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>-38.452484357348936,174.64322567628707</t>
+        </is>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>-38.451781494484166,174.64308859636998</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>-38.45107674947826,174.64296260771334</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>-38.46371412509806,174.64391853316846</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>-38.463005417514296,174.6441868626086</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>-38.46229975747307,174.64429629367731</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>-38.46159500896497,174.64435795188655</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>-38.460892273288906,174.64431456041234</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-38.46019099309992,174.6441951048083</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>-38.45948866865662,174.64412960634004</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>-38.45878693849198,174.644032835912</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>-38.45808534771423,174.64390538210858</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>-38.45738213319673,174.64382472425336</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>-38.45667821870138,174.64377671507432</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>-38.45597793238571,174.64369132102743</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>-38.455282980383366,174.64352232901712</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>-38.45457848476159,174.64350260417416</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>-38.453878214352564,174.64341664060922</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>-38.453182807717525,174.6433148406635</t>
+        </is>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>-38.45249177852117,174.64318941751156</t>
+        </is>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>-38.45179065547915,174.64304950621846</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>-38.45106558130539,174.64301026209478</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0259/nzd0259.xlsx
+++ b/data/nzd0259/nzd0259.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U348"/>
+  <dimension ref="A1:U349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24406,7 +24406,7 @@
         <v>357.69</v>
       </c>
       <c r="S348" t="n">
-        <v>347.98</v>
+        <v>339.19</v>
       </c>
       <c r="T348" t="n">
         <v>329.08</v>
@@ -24414,6 +24414,75 @@
       <c r="U348" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:42+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>349.8</v>
+      </c>
+      <c r="C349" t="n">
+        <v>323.7</v>
+      </c>
+      <c r="D349" t="n">
+        <v>312.41</v>
+      </c>
+      <c r="E349" t="n">
+        <v>308.06</v>
+      </c>
+      <c r="F349" t="n">
+        <v>312.77</v>
+      </c>
+      <c r="G349" t="n">
+        <v>322.47</v>
+      </c>
+      <c r="H349" t="n">
+        <v>326.09</v>
+      </c>
+      <c r="I349" t="n">
+        <v>333.06</v>
+      </c>
+      <c r="J349" t="n">
+        <v>341.88</v>
+      </c>
+      <c r="K349" t="n">
+        <v>348.82</v>
+      </c>
+      <c r="L349" t="n">
+        <v>349.04</v>
+      </c>
+      <c r="M349" t="n">
+        <v>349.7</v>
+      </c>
+      <c r="N349" t="n">
+        <v>359.24</v>
+      </c>
+      <c r="O349" t="n">
+        <v>355.2</v>
+      </c>
+      <c r="P349" t="n">
+        <v>356.8</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>363.25</v>
+      </c>
+      <c r="R349" t="n">
+        <v>360.18</v>
+      </c>
+      <c r="S349" t="n">
+        <v>327.63</v>
+      </c>
+      <c r="T349" t="n">
+        <v>328.19</v>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -24428,7 +24497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B357"/>
+  <dimension ref="A1:B358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28001,6 +28070,16 @@
       </c>
       <c r="B357" t="n">
         <v>1.64</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>-0.78</v>
       </c>
     </row>
   </sheetData>
@@ -28169,28 +28248,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07016659695547722</v>
+        <v>-0.0679522393755652</v>
       </c>
       <c r="J2" t="n">
+        <v>348</v>
+      </c>
+      <c r="K2" t="n">
         <v>347</v>
       </c>
-      <c r="K2" t="n">
-        <v>346</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.008159764386490798</v>
+        <v>0.007687828778656702</v>
       </c>
       <c r="M2" t="n">
-        <v>3.982483873651876</v>
+        <v>3.983231858402356</v>
       </c>
       <c r="N2" t="n">
-        <v>33.15132811366412</v>
+        <v>33.10464911790186</v>
       </c>
       <c r="O2" t="n">
-        <v>5.757719002666257</v>
+        <v>5.753663973321857</v>
       </c>
       <c r="P2" t="n">
-        <v>347.519097440456</v>
+        <v>347.4952805877093</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -28251,28 +28330,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04761582030446946</v>
+        <v>-0.04623855501705622</v>
       </c>
       <c r="J3" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K3" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004724119283816552</v>
+        <v>0.004477558158650918</v>
       </c>
       <c r="M3" t="n">
-        <v>4.21584173003803</v>
+        <v>4.211928868633591</v>
       </c>
       <c r="N3" t="n">
-        <v>26.45377957909156</v>
+        <v>26.39663366132994</v>
       </c>
       <c r="O3" t="n">
-        <v>5.143323787113889</v>
+        <v>5.137765434634978</v>
       </c>
       <c r="P3" t="n">
-        <v>322.3888893127286</v>
+        <v>322.3740876652246</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -28333,28 +28412,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01824731249101736</v>
+        <v>0.02317313725990815</v>
       </c>
       <c r="J4" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K4" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003295272489654</v>
+        <v>0.0005320069286702811</v>
       </c>
       <c r="M4" t="n">
-        <v>6.000445878059021</v>
+        <v>6.012841125185623</v>
       </c>
       <c r="N4" t="n">
-        <v>55.94044486380398</v>
+        <v>56.0210815810623</v>
       </c>
       <c r="O4" t="n">
-        <v>7.479334520116344</v>
+        <v>7.484723213390212</v>
       </c>
       <c r="P4" t="n">
-        <v>302.7281624765465</v>
+        <v>302.6752240030642</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -28415,28 +28494,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2610715695242858</v>
+        <v>0.2619676197629935</v>
       </c>
       <c r="J5" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K5" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0779292825061243</v>
+        <v>0.07881333311168703</v>
       </c>
       <c r="M5" t="n">
-        <v>4.750429151043541</v>
+        <v>4.741464117621603</v>
       </c>
       <c r="N5" t="n">
-        <v>44.66273121184792</v>
+        <v>44.54237764847771</v>
       </c>
       <c r="O5" t="n">
-        <v>6.683018121466373</v>
+        <v>6.674007615254698</v>
       </c>
       <c r="P5" t="n">
-        <v>299.4824055226955</v>
+        <v>299.4727755553242</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -28497,28 +28576,28 @@
         <v>0.1324</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3849399289250754</v>
+        <v>0.3924340401247038</v>
       </c>
       <c r="J6" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K6" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05037535762475209</v>
+        <v>0.05234956417844527</v>
       </c>
       <c r="M6" t="n">
-        <v>9.968836013778347</v>
+        <v>9.972579003476046</v>
       </c>
       <c r="N6" t="n">
-        <v>153.2021122302814</v>
+        <v>153.3107834756979</v>
       </c>
       <c r="O6" t="n">
-        <v>12.37748408321665</v>
+        <v>12.38187318121527</v>
       </c>
       <c r="P6" t="n">
-        <v>288.7143469923323</v>
+        <v>288.6330942862123</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28575,28 +28654,28 @@
         <v>0.1253</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3957854716551596</v>
+        <v>0.4007152580975858</v>
       </c>
       <c r="J7" t="n">
+        <v>348</v>
+      </c>
+      <c r="K7" t="n">
         <v>347</v>
       </c>
-      <c r="K7" t="n">
-        <v>346</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1177635992665437</v>
+        <v>0.1205539952305736</v>
       </c>
       <c r="M7" t="n">
-        <v>5.846805338912305</v>
+        <v>5.855802458244073</v>
       </c>
       <c r="N7" t="n">
-        <v>65.05444780930527</v>
+        <v>65.10933104912644</v>
       </c>
       <c r="O7" t="n">
-        <v>8.065633751250132</v>
+        <v>8.069035323328709</v>
       </c>
       <c r="P7" t="n">
-        <v>302.7903934643895</v>
+        <v>302.7373961732261</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28653,28 +28732,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2519201540886671</v>
+        <v>0.2557189286532476</v>
       </c>
       <c r="J8" t="n">
+        <v>348</v>
+      </c>
+      <c r="K8" t="n">
         <v>347</v>
       </c>
-      <c r="K8" t="n">
-        <v>346</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.0644566480286195</v>
+        <v>0.06645498693457419</v>
       </c>
       <c r="M8" t="n">
-        <v>5.474836416341284</v>
+        <v>5.477151687418471</v>
       </c>
       <c r="N8" t="n">
-        <v>51.02676397076397</v>
+        <v>51.02350221387182</v>
       </c>
       <c r="O8" t="n">
-        <v>7.143302035526985</v>
+        <v>7.143073723116109</v>
       </c>
       <c r="P8" t="n">
-        <v>312.3322743525106</v>
+        <v>312.2914160669099</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28731,28 +28810,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2984191501342977</v>
+        <v>0.3032703267434003</v>
       </c>
       <c r="J9" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K9" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05499047877125107</v>
+        <v>0.05683873718323629</v>
       </c>
       <c r="M9" t="n">
-        <v>6.936391527416242</v>
+        <v>6.940550718244529</v>
       </c>
       <c r="N9" t="n">
-        <v>85.10755086410836</v>
+        <v>85.09694772334595</v>
       </c>
       <c r="O9" t="n">
-        <v>9.225375377951206</v>
+        <v>9.224800687459103</v>
       </c>
       <c r="P9" t="n">
-        <v>316.1048730531573</v>
+        <v>316.0527391102656</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28809,28 +28888,28 @@
         <v>0.1406</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5173857110041566</v>
+        <v>0.5216315127914527</v>
       </c>
       <c r="J10" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K10" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1776967788298391</v>
+        <v>0.1805358620057554</v>
       </c>
       <c r="M10" t="n">
-        <v>6.460443056171434</v>
+        <v>6.465694183677902</v>
       </c>
       <c r="N10" t="n">
-        <v>67.85971793096314</v>
+        <v>67.83949890068729</v>
       </c>
       <c r="O10" t="n">
-        <v>8.237701010049051</v>
+        <v>8.236473693316047</v>
       </c>
       <c r="P10" t="n">
-        <v>320.3496361100005</v>
+        <v>320.3035420049957</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28887,28 +28966,28 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3618983129065263</v>
+        <v>0.3664626411983748</v>
       </c>
       <c r="J11" t="n">
+        <v>348</v>
+      </c>
+      <c r="K11" t="n">
         <v>347</v>
       </c>
-      <c r="K11" t="n">
-        <v>346</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.08793462647129335</v>
+        <v>0.09019503606668211</v>
       </c>
       <c r="M11" t="n">
-        <v>6.255922984997056</v>
+        <v>6.261153775054598</v>
       </c>
       <c r="N11" t="n">
-        <v>75.38219362487634</v>
+        <v>75.37291552164557</v>
       </c>
       <c r="O11" t="n">
-        <v>8.682291956901492</v>
+        <v>8.681757628593738</v>
       </c>
       <c r="P11" t="n">
-        <v>330.7101252035438</v>
+        <v>330.6610941526169</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28965,28 +29044,28 @@
         <v>0.1507</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3941206554585569</v>
+        <v>0.3985288099092645</v>
       </c>
       <c r="J12" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K12" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L12" t="n">
-        <v>0.09952177013970831</v>
+        <v>0.1018143647834399</v>
       </c>
       <c r="M12" t="n">
-        <v>6.866443957855641</v>
+        <v>6.870188859504426</v>
       </c>
       <c r="N12" t="n">
-        <v>77.83520674308484</v>
+        <v>77.80485763797427</v>
       </c>
       <c r="O12" t="n">
-        <v>8.822426352375226</v>
+        <v>8.82070618703368</v>
       </c>
       <c r="P12" t="n">
-        <v>330.3728650598359</v>
+        <v>330.3254900559648</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29043,28 +29122,28 @@
         <v>0.1363</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2782829815241739</v>
+        <v>0.2830661400871027</v>
       </c>
       <c r="J13" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K13" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04642649817862543</v>
+        <v>0.04809696487334025</v>
       </c>
       <c r="M13" t="n">
-        <v>7.738673340194424</v>
+        <v>7.741333610078958</v>
       </c>
       <c r="N13" t="n">
-        <v>86.80283449825755</v>
+        <v>86.77515597221281</v>
       </c>
       <c r="O13" t="n">
-        <v>9.316803877846606</v>
+        <v>9.315318350556399</v>
       </c>
       <c r="P13" t="n">
-        <v>333.5105650275161</v>
+        <v>333.4585981089913</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29121,28 +29200,28 @@
         <v>0.0713</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5058304662231815</v>
+        <v>0.5116982205847179</v>
       </c>
       <c r="J14" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K14" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1486059594780673</v>
+        <v>0.1517210393422203</v>
       </c>
       <c r="M14" t="n">
-        <v>7.178216106129422</v>
+        <v>7.188116587925339</v>
       </c>
       <c r="N14" t="n">
-        <v>81.18333936492924</v>
+        <v>81.29258218556609</v>
       </c>
       <c r="O14" t="n">
-        <v>9.010179763186152</v>
+        <v>9.0162399139312</v>
       </c>
       <c r="P14" t="n">
-        <v>334.8952354519357</v>
+        <v>334.8321739397539</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29199,28 +29278,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4466963895285026</v>
+        <v>0.4498052023102033</v>
       </c>
       <c r="J15" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K15" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1143015041767794</v>
+        <v>0.1161684629629215</v>
       </c>
       <c r="M15" t="n">
-        <v>7.24969666963799</v>
+        <v>7.244622715592608</v>
       </c>
       <c r="N15" t="n">
-        <v>85.62910618956694</v>
+        <v>85.47919386392778</v>
       </c>
       <c r="O15" t="n">
-        <v>9.253599634173014</v>
+        <v>9.245495869012531</v>
       </c>
       <c r="P15" t="n">
-        <v>337.5746409933211</v>
+        <v>337.5412301817866</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29277,28 +29356,28 @@
         <v>0.079</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2741384168598651</v>
+        <v>0.2776816281223002</v>
       </c>
       <c r="J16" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K16" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L16" t="n">
-        <v>0.03828535641032582</v>
+        <v>0.03940738559330037</v>
       </c>
       <c r="M16" t="n">
-        <v>8.193842049827193</v>
+        <v>8.188904709011007</v>
       </c>
       <c r="N16" t="n">
-        <v>104.5480411431469</v>
+        <v>104.3725112049456</v>
       </c>
       <c r="O16" t="n">
-        <v>10.22487364925098</v>
+        <v>10.21628656630899</v>
       </c>
       <c r="P16" t="n">
-        <v>342.9285961089065</v>
+        <v>342.8905167609274</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29355,28 +29434,28 @@
         <v>0.1836</v>
       </c>
       <c r="I17" t="n">
-        <v>0.360653178311276</v>
+        <v>0.3671937216867872</v>
       </c>
       <c r="J17" t="n">
+        <v>348</v>
+      </c>
+      <c r="K17" t="n">
         <v>347</v>
       </c>
-      <c r="K17" t="n">
-        <v>346</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.04733623124259845</v>
+        <v>0.04910578985199232</v>
       </c>
       <c r="M17" t="n">
-        <v>9.955393034518965</v>
+        <v>9.962959953087566</v>
       </c>
       <c r="N17" t="n">
-        <v>145.2630330090082</v>
+        <v>145.2714363505476</v>
       </c>
       <c r="O17" t="n">
-        <v>12.05251148138877</v>
+        <v>12.05286009005944</v>
       </c>
       <c r="P17" t="n">
-        <v>341.4832407543956</v>
+        <v>341.4129807523034</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29433,28 +29512,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4876428563718345</v>
+        <v>0.4938529203951524</v>
       </c>
       <c r="J18" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K18" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L18" t="n">
-        <v>0.06902025027358172</v>
+        <v>0.07089530762496898</v>
       </c>
       <c r="M18" t="n">
-        <v>10.00854566791883</v>
+        <v>10.00993004672052</v>
       </c>
       <c r="N18" t="n">
-        <v>170.1910801370067</v>
+        <v>170.055891248094</v>
       </c>
       <c r="O18" t="n">
-        <v>13.04573034126517</v>
+        <v>13.04054796579093</v>
       </c>
       <c r="P18" t="n">
-        <v>336.0948260398194</v>
+        <v>336.0259689709895</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -29515,28 +29594,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.705211889217473</v>
+        <v>1.698949546551924</v>
       </c>
       <c r="J19" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K19" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1447371429640548</v>
+        <v>0.1446005961396599</v>
       </c>
       <c r="M19" t="n">
-        <v>26.43194032823588</v>
+        <v>26.34665997894334</v>
       </c>
       <c r="N19" t="n">
-        <v>942.6978185837503</v>
+        <v>939.2923879715449</v>
       </c>
       <c r="O19" t="n">
-        <v>30.70338448092897</v>
+        <v>30.64787738117511</v>
       </c>
       <c r="P19" t="n">
-        <v>285.359163041642</v>
+        <v>285.4270136562607</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -29597,28 +29676,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9557268405987314</v>
+        <v>0.9647459415091267</v>
       </c>
       <c r="J20" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K20" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L20" t="n">
-        <v>0.06041378057544333</v>
+        <v>0.06175195058756178</v>
       </c>
       <c r="M20" t="n">
-        <v>23.70869712129472</v>
+        <v>23.67931641251078</v>
       </c>
       <c r="N20" t="n">
-        <v>775.3208981565524</v>
+        <v>773.86296897556</v>
       </c>
       <c r="O20" t="n">
-        <v>27.84458471869445</v>
+        <v>27.81839263824493</v>
       </c>
       <c r="P20" t="n">
-        <v>286.2814528758184</v>
+        <v>286.1832769376821</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -29660,7 +29739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U348"/>
+  <dimension ref="A1:U349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66757,7 +66836,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>-38.45179065547915,174.64304950621846</t>
+          <t>-38.45176803603287,174.64314602373676</t>
         </is>
       </c>
       <c r="T348" t="inlineStr">
@@ -66768,6 +66847,113 @@
       <c r="U348" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:42+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>-38.46371356795436,174.64394751708588</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>-38.46300449030186,174.64423509228385</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>-38.46229866723555,174.64435300022134</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-38.461594365825285,174.64439140269326</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-38.46089205304248,174.6443260160573</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-38.46019083232981,174.64420346734872</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>-38.45948826564367,174.64415056976617</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>-38.458786429795566,174.6440592976867</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>-38.45808440653503,174.64394684506172</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>-38.45738108278844,174.64384806142135</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>-38.45667780277901,174.64378322491024</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>-38.455976524101395,174.6437133628921</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>-38.45528171806355,174.6435420865651</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>-38.45457699624896,174.6435259018658</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>-38.45387638291819,174.64344530563181</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>-38.45318334659874,174.64331030904594</t>
+        </is>
+      </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>-38.452497429498116,174.643161807613</t>
+        </is>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>-38.451738288382515,174.643272956805</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>-38.45106329105561,174.64302003453517</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
